--- a/data/AAGYO (TRY).xlsx
+++ b/data/AAGYO (TRY).xlsx
@@ -403,958 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E108"/>
-  <cols>
-    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
-    <col min="2" max="2" customWidth="1" width="20"/>
-    <col min="3" max="3" customWidth="1" width="20"/>
-    <col min="4" max="4" customWidth="1" width="20"/>
-    <col min="5" max="5" customWidth="1" width="20"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Kalem</v>
-      </c>
-      <c r="B1" t="str">
-        <v>2026/3</v>
-      </c>
-      <c r="C1" t="str">
-        <v>2025/12</v>
-      </c>
-      <c r="D1" t="str">
-        <v>2024/12</v>
-      </c>
-      <c r="E1" t="str">
-        <v>2023/12</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Dönen Varlıklar</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B3">
-        <v>488477842</v>
-      </c>
-      <c r="C3">
-        <v>88060332</v>
-      </c>
-      <c r="D3">
-        <v>21238281.85896462</v>
-      </c>
-      <c r="E3">
-        <v>269050.98837464105</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve">    Gayrimenkul Projeleri Kapsamında Açılan Nakit Hesapları</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlar</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v xml:space="preserve">    Teminata Verilen Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v xml:space="preserve">    Ticari Alacaklar</v>
-      </c>
-      <c r="B7">
-        <v>12570925</v>
-      </c>
-      <c r="C7">
-        <v>168181718</v>
-      </c>
-      <c r="D7">
-        <v>33140951.75672976</v>
-      </c>
-      <c r="E7">
-        <v>6710704.837896678</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabı</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v xml:space="preserve">    Diğer Alacaklar</v>
-      </c>
-      <c r="B10">
-        <v>1572991</v>
-      </c>
-      <c r="C10">
-        <v>1044622</v>
-      </c>
-      <c r="D10">
-        <v>49512.3893484961</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v xml:space="preserve">    Stoklar</v>
-      </c>
-      <c r="B14">
-        <v>1301418127</v>
-      </c>
-      <c r="C14">
-        <v>1318818427</v>
-      </c>
-      <c r="D14">
-        <v>1412340086.3514302</v>
-      </c>
-      <c r="E14">
-        <v>1143747838.6163063</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v xml:space="preserve">    Proje Halindeki Stoklar</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
-      </c>
-      <c r="B17">
-        <v>23838347</v>
-      </c>
-      <c r="C17">
-        <v>5099555</v>
-      </c>
-      <c r="D17">
-        <v>4637683.577838679</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v xml:space="preserve">    Ertelenmiş Sigortacılık Üretim Giderleri</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
-      </c>
-      <c r="D19">
-        <v>392740.6267164124</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
-      </c>
-      <c r="B21">
-        <v>923567</v>
-      </c>
-      <c r="C21">
-        <v>22552697</v>
-      </c>
-      <c r="D21">
-        <v>7750983.312996781</v>
-      </c>
-      <c r="E21">
-        <v>545178.7909000617</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
-      </c>
-      <c r="B24">
-        <v>1828801799</v>
-      </c>
-      <c r="C24">
-        <v>1603757351</v>
-      </c>
-      <c r="D24">
-        <v>1479550239.8740249</v>
-      </c>
-      <c r="E24">
-        <v>1151272773.2334776</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlar</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve Bağlı Ortaklıklardaki Yatırımlar</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v xml:space="preserve">    Ticari Alacaklar</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>1542682</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v xml:space="preserve">    Diğer Alacaklar</v>
-      </c>
-      <c r="B30">
-        <v>6294</v>
-      </c>
-      <c r="C30">
-        <v>9582</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v xml:space="preserve">    Stoklar</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
-      </c>
-      <c r="B37">
-        <v>15449915301</v>
-      </c>
-      <c r="C37">
-        <v>15449915301</v>
-      </c>
-      <c r="D37">
-        <v>15267588407.669645</v>
-      </c>
-      <c r="E37">
-        <v>14118095723.348701</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v xml:space="preserve">    Proje Halindeki Yatırım Amaçlı Gayrimenkuller</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v xml:space="preserve">    Maddi Duran Varlıklar</v>
-      </c>
-      <c r="B39">
-        <v>109282898</v>
-      </c>
-      <c r="C39">
-        <v>109855011</v>
-      </c>
-      <c r="D39">
-        <v>92257428.53407212</v>
-      </c>
-      <c r="E39">
-        <v>79149274.90049432</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v xml:space="preserve">    Diğer Duran Varlıklar</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v xml:space="preserve">    Toplam Duran Varlıklar</v>
-      </c>
-      <c r="B47">
-        <v>15559204493</v>
-      </c>
-      <c r="C47">
-        <v>15561322576</v>
-      </c>
-      <c r="D47">
-        <v>15359845836.203718</v>
-      </c>
-      <c r="E47">
-        <v>14197244998.249195</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v xml:space="preserve">    Toplam Varlıklar</v>
-      </c>
-      <c r="B48">
-        <v>17388006292</v>
-      </c>
-      <c r="C48">
-        <v>17165079927</v>
-      </c>
-      <c r="D48">
-        <v>16839396076.077744</v>
-      </c>
-      <c r="E48">
-        <v>15348517771.482674</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Kısa Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v xml:space="preserve">    Finansal Borçlar</v>
-      </c>
-      <c r="B50">
-        <v>350756209</v>
-      </c>
-      <c r="C50">
-        <v>417776502</v>
-      </c>
-      <c r="D50">
-        <v>820246802.2667372</v>
-      </c>
-      <c r="E50">
-        <v>186512813.03862125</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v xml:space="preserve">    Ticari Borçlar</v>
-      </c>
-      <c r="B52">
-        <v>27502639</v>
-      </c>
-      <c r="C52">
-        <v>14691511</v>
-      </c>
-      <c r="D52">
-        <v>39689219.99577104</v>
-      </c>
-      <c r="E52">
-        <v>51218175.5639224</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
-      </c>
-      <c r="B54">
-        <v>4535309</v>
-      </c>
-      <c r="C54">
-        <v>1752750</v>
-      </c>
-      <c r="D54">
-        <v>698203.4800319875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v xml:space="preserve">    Diğer Borçlar</v>
-      </c>
-      <c r="B55">
-        <v>3949408</v>
-      </c>
-      <c r="C55">
-        <v>1010839</v>
-      </c>
-      <c r="D55">
-        <v>988990.004576151</v>
-      </c>
-      <c r="E55">
-        <v>1151616.9764447745</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
-      </c>
-      <c r="B56">
-        <v>1189032</v>
-      </c>
-      <c r="C56">
-        <v>49310164</v>
-      </c>
-      <c r="D56">
-        <v>14953094.818721239</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
-      </c>
-      <c r="B60">
-        <v>16940431</v>
-      </c>
-      <c r="C60">
-        <v>22166581</v>
-      </c>
-      <c r="D60">
-        <v>22980936.61447919</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
-      </c>
-      <c r="B61">
-        <v>14712703</v>
-      </c>
-      <c r="C61">
-        <v>12153386</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
-      </c>
-      <c r="B62">
-        <v>1148870</v>
-      </c>
-      <c r="C62">
-        <v>627458</v>
-      </c>
-      <c r="D62">
-        <v>1199346.682085564</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
-      </c>
-      <c r="B63">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v xml:space="preserve">    Satış Amaçlı Sınıflandırılan Varlık Gruplarına İlişkin Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Varlık Gruplarına İlişkin Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
-      </c>
-      <c r="B66">
-        <v>420735799</v>
-      </c>
-      <c r="C66">
-        <v>519489191</v>
-      </c>
-      <c r="D66">
-        <v>900756593.8624024</v>
-      </c>
-      <c r="E66">
-        <v>238882605.5789884</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Uzun Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v xml:space="preserve">    Finansal Borçlar</v>
-      </c>
-      <c r="E68">
-        <v>971070133.4179808</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v xml:space="preserve">    Ticari Borçlar</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v xml:space="preserve">    Diğer Borçlar</v>
-      </c>
-      <c r="B73">
-        <v>4436918</v>
-      </c>
-      <c r="C73">
-        <v>6222964</v>
-      </c>
-      <c r="D73">
-        <v>2847496.0922287963</v>
-      </c>
-      <c r="E73">
-        <v>1747482.307011927</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v xml:space="preserve">    Türev Araçlar</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
-      </c>
-      <c r="B80">
-        <v>5850522</v>
-      </c>
-      <c r="C80">
-        <v>5630619</v>
-      </c>
-      <c r="D80">
-        <v>6493331.869448785</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Borçlar</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
-      </c>
-      <c r="B82">
-        <v>3295338106</v>
-      </c>
-      <c r="C82">
-        <v>3080276809</v>
-      </c>
-      <c r="D82">
-        <v>2528938959.4007463</v>
-      </c>
-      <c r="E82">
-        <v>1659395871.9673464</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
-      </c>
-      <c r="B84">
-        <v>3305625546</v>
-      </c>
-      <c r="C84">
-        <v>3092130392</v>
-      </c>
-      <c r="D84">
-        <v>2538279787.362424</v>
-      </c>
-      <c r="E84">
-        <v>2632213487.6923394</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Özkaynaklar</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
-      </c>
-      <c r="B86">
-        <v>13661644947</v>
-      </c>
-      <c r="C86">
-        <v>13553460344</v>
-      </c>
-      <c r="D86">
-        <v>13400359694.852917</v>
-      </c>
-      <c r="E86">
-        <v>12477421678.211346</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v xml:space="preserve">    Ödenmiş Sermaye</v>
-      </c>
-      <c r="B87">
-        <v>595348000</v>
-      </c>
-      <c r="C87">
-        <v>595348000</v>
-      </c>
-      <c r="D87">
-        <v>595348000</v>
-      </c>
-      <c r="E87">
-        <v>210971707</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
-      </c>
-      <c r="B88">
-        <v>473807725</v>
-      </c>
-      <c r="C88">
-        <v>473807725</v>
-      </c>
-      <c r="D88">
-        <v>473807725.01116437</v>
-      </c>
-      <c r="E88">
-        <v>227762031.72629324</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v xml:space="preserve">    Birleşme Denkleştirme Hesabı</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v xml:space="preserve">    Sermaye Avansı</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v xml:space="preserve">    Karşılıklı İştirak Sermaye Düzeltmesi (-)</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi Teşebbüs veya İşletmeleri İçeren Birleşmelerin Etkisi</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v xml:space="preserve">    Pay Bazlı Ödemeler (-)</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
-      </c>
-      <c r="B97">
-        <v>24838994</v>
-      </c>
-      <c r="C97">
-        <v>25001439</v>
-      </c>
-      <c r="D97">
-        <v>10137152.773910247</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
-      </c>
-      <c r="B99">
-        <v>44487013</v>
-      </c>
-      <c r="C99">
-        <v>12654789</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v xml:space="preserve">    Diğer Özkaynak Payları</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v xml:space="preserve">    Diğer Yedekler</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v xml:space="preserve">    Ödenen Kar Payı Avansları (Net) (-)</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
-      </c>
-      <c r="B103">
-        <v>12414816167</v>
-      </c>
-      <c r="C103">
-        <v>12308412028</v>
-      </c>
-      <c r="D103">
-        <v>11808820922.22949</v>
-      </c>
-      <c r="E103">
-        <v>12066023718.199968</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
-      </c>
-      <c r="B104">
-        <v>108347048</v>
-      </c>
-      <c r="C104">
-        <v>138236363</v>
-      </c>
-      <c r="D104">
-        <v>512245894.838352</v>
-      </c>
-      <c r="E104">
-        <v>-27335778.71491546</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v xml:space="preserve">    Azınlık Payları</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v xml:space="preserve">    Toplam Özkaynaklar</v>
-      </c>
-      <c r="B106">
-        <v>13661644947</v>
-      </c>
-      <c r="C106">
-        <v>13553460344</v>
-      </c>
-      <c r="D106">
-        <v>13400359694.852917</v>
-      </c>
-      <c r="E106">
-        <v>12477421678.211346</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v xml:space="preserve">    Toplam Kaynaklar</v>
-      </c>
-      <c r="B107">
-        <v>17388006292</v>
-      </c>
-      <c r="C107">
-        <v>17165079927</v>
-      </c>
-      <c r="D107">
-        <v>16839396076.077744</v>
-      </c>
-      <c r="E107">
-        <v>15348517771.482674</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E108"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1369,13 +418,13 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
-      </c>
-      <c r="D1" t="str">
-        <v>2025/3</v>
       </c>
       <c r="E1" t="str">
         <v>2024/12</v>
@@ -1386,556 +435,1062 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>Dönen Varlıklar</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">    Satış Gelirleri</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>360563785</v>
+        <v>2116920003</v>
       </c>
       <c r="C3">
-        <v>1432494159.7869642</v>
+        <v>522736754.15131617</v>
       </c>
       <c r="D3">
-        <v>717521685</v>
+        <v>94236357</v>
       </c>
       <c r="E3">
-        <v>755403349.5382925</v>
+        <v>22727807.83105807</v>
       </c>
       <c r="F3">
-        <v>6710704.837896678</v>
+        <v>287920.6143482827</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">    Toplam Hasılat</v>
+        <v xml:space="preserve">    Gayrimenkul Projeleri Kapsamında Açılan Nakit Hesapları</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">    Yurt İçi Satışlar</v>
+        <v xml:space="preserve">    Finansal Yatırımlar</v>
+      </c>
+      <c r="B5">
+        <v>88743270</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">    Yurt Dışı Satışlar</v>
+        <v xml:space="preserve">    Teminata Verilen Finansal Varlıklar</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">    Satışların Maliyeti (-)</v>
+        <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>-23483744</v>
+        <v>32773803</v>
       </c>
       <c r="C7">
-        <v>-517877731.60098696</v>
+        <v>13452574.438739095</v>
       </c>
       <c r="D7">
-        <v>-310048709</v>
+        <v>179976976</v>
       </c>
       <c r="E7">
-        <v>-267838930.71755072</v>
+        <v>35465259.754399</v>
+      </c>
+      <c r="F7">
+        <v>7181353.509643215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
-      </c>
-      <c r="B8">
-        <v>337080041</v>
-      </c>
-      <c r="C8">
-        <v>914616428.1859773</v>
-      </c>
-      <c r="D8">
-        <v>407472976</v>
-      </c>
-      <c r="E8">
-        <v>487564418.8207418</v>
-      </c>
-      <c r="F8">
-        <v>6710704.837896678</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
+        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabı</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
+        <v xml:space="preserve">    Diğer Alacaklar</v>
+      </c>
+      <c r="B10">
+        <v>4185592</v>
+      </c>
+      <c r="C10">
+        <v>1683311.1739165294</v>
+      </c>
+      <c r="D10">
+        <v>1117885</v>
+      </c>
+      <c r="E10">
+        <v>52984.89199088186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">    Canlı Varlıklar Gerçeğe Uygun Değer Farkları</v>
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">    Brüt Kar (Zarar)</v>
-      </c>
-      <c r="B13">
-        <v>337080041</v>
-      </c>
-      <c r="C13">
-        <v>914616428.1859773</v>
-      </c>
-      <c r="D13">
-        <v>407472976</v>
-      </c>
-      <c r="E13">
-        <v>487564418.8207418</v>
-      </c>
-      <c r="F13">
-        <v>6710704.837896678</v>
-      </c>
-    </row>
-    <row r="14"/>
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">    Stoklar</v>
+      </c>
+      <c r="B14">
+        <v>1382513153</v>
+      </c>
+      <c r="C14">
+        <v>1392691805.049502</v>
+      </c>
+      <c r="D14">
+        <v>1411312458</v>
+      </c>
+      <c r="E14">
+        <v>1511393166.7286072</v>
+      </c>
+      <c r="F14">
+        <v>1223963466.3425968</v>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
-      </c>
-      <c r="B15">
-        <v>-35274297</v>
-      </c>
-      <c r="C15">
-        <v>-138182245.05077308</v>
-      </c>
-      <c r="D15">
-        <v>-39012411</v>
-      </c>
-      <c r="E15">
-        <v>-133575005.74914268</v>
-      </c>
-      <c r="F15">
-        <v>-3584001.9622695204</v>
+        <v xml:space="preserve">    Proje Halindeki Stoklar</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
-      </c>
-      <c r="B16">
-        <v>-1125701</v>
-      </c>
-      <c r="C16">
-        <v>-5359354.658333974</v>
-      </c>
-      <c r="D16">
-        <v>-365307</v>
-      </c>
-      <c r="E16">
-        <v>-10903122.444120016</v>
+        <v xml:space="preserve">    Canlı Varlıklar</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
+        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
+      </c>
+      <c r="B17">
+        <v>17393178</v>
+      </c>
+      <c r="C17">
+        <v>25510225.978915058</v>
+      </c>
+      <c r="D17">
+        <v>5457207</v>
+      </c>
+      <c r="E17">
+        <v>4962942.946059473</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
-      </c>
-      <c r="B18">
-        <v>10141665</v>
-      </c>
-      <c r="C18">
-        <v>10248779.585829869</v>
-      </c>
-      <c r="D18">
-        <v>7318603</v>
-      </c>
-      <c r="E18">
-        <v>2376316.281951239</v>
+        <v xml:space="preserve">    Ertelenmiş Sigortacılık Üretim Giderleri</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
-        <v>-1888316</v>
-      </c>
-      <c r="C19">
-        <v>-26121848.13951</v>
+        <v>24645509</v>
       </c>
       <c r="D19">
-        <v>-60887965</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>-4757596.567733012</v>
+        <v>420285.10360371904</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">    Diğer Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+        <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>308933392</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>755201759.9231901</v>
+        <v>988340.4615541776</v>
       </c>
       <c r="D21">
-        <v>314525896</v>
+        <v>24134408</v>
       </c>
       <c r="E21">
-        <v>340705010.34169734</v>
+        <v>8294590.890607793</v>
       </c>
       <c r="F21">
-        <v>3126702.8756271577</v>
-      </c>
-    </row>
-    <row r="22"/>
+        <v>583414.368235023</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    Ödenecek Kar Paylarının Defter Değeri ile Dağıtılan Nakit Dışı Varlıkların Değeri Arasındaki Fark</v>
+        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıklar</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Finansal Tablo Dışı Bırakılmasından Kaynaklanan Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
+      </c>
+      <c r="B24">
+        <v>3667174508</v>
+      </c>
+      <c r="C24">
+        <v>1957063011.253943</v>
+      </c>
+      <c r="D24">
+        <v>1716235291</v>
+      </c>
+      <c r="E24">
+        <v>1583317038.146326</v>
+      </c>
+      <c r="F24">
+        <v>1232016154.8348234</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>888624424.3452888</v>
-      </c>
-      <c r="D25">
-        <v>684518774</v>
-      </c>
-      <c r="E25">
-        <v>709751376.0643222</v>
+        <v>Duran Varlıklar</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>-803243578.2676934</v>
-      </c>
-      <c r="D26">
-        <v>-31974282</v>
-      </c>
-      <c r="E26">
-        <v>-117927721.78999792</v>
+        <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">    TFRS 9 Uyarınca Belirlenen Değer Düşüklüğü Kazançları (Zararları) ve Değer Düşüklüğü Zararlarının İptalleri</v>
+        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve Bağlı Ortaklıklardaki Yatırımlar</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
+        <v xml:space="preserve">    Ticari Alacaklar</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>1650876</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">    İştirakler, Müşterek Kontrol Edilen İşletmeler ve Bağlı Ortaklıklardan Diğer Gelirler (Giderler)</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Diğer Alacaklar</v>
+      </c>
+      <c r="B30">
+        <v>9027</v>
+      </c>
+      <c r="C30">
+        <v>6735.423488520046</v>
+      </c>
+      <c r="D30">
+        <v>10255</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">    Risk Pozisyonlarını Netleştiren Kalemler Grubuna Yönelik Finansal Riskten Korunma Kazançları (Kayıpları)</v>
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
-      </c>
-      <c r="B33">
-        <v>308933392</v>
-      </c>
-      <c r="C33">
-        <v>840582606.0007855</v>
-      </c>
-      <c r="D33">
-        <v>967070388</v>
-      </c>
-      <c r="E33">
-        <v>932528664.6160216</v>
-      </c>
-      <c r="F33">
-        <v>3126702.8756271577</v>
-      </c>
-    </row>
-    <row r="34"/>
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve">    Stoklar</v>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
-      </c>
-      <c r="B35">
-        <v>22092456</v>
-      </c>
-      <c r="C35">
-        <v>12163162.90392075</v>
-      </c>
-      <c r="D35">
-        <v>857856</v>
-      </c>
-      <c r="E35">
-        <v>4635173.515161347</v>
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
-      </c>
-      <c r="B36">
-        <v>-6830472</v>
-      </c>
-      <c r="C36">
-        <v>-225502630.09433472</v>
-      </c>
-      <c r="D36">
-        <v>-74081442</v>
-      </c>
-      <c r="E36">
-        <v>-166301099.496538</v>
-      </c>
-      <c r="F36">
-        <v>-30533724.01395043</v>
+        <v xml:space="preserve">    Canlı Varlıklar</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkuller</v>
       </c>
       <c r="B37">
-        <v>298827074</v>
+        <v>16533479888</v>
       </c>
       <c r="C37">
-        <v>721433455.3595893</v>
+        <v>16533479887.829784</v>
       </c>
       <c r="D37">
-        <v>298809703</v>
+        <v>16533479888</v>
       </c>
       <c r="E37">
-        <v>886775520.5403728</v>
+        <v>16338365677.482443</v>
+      </c>
+      <c r="F37">
+        <v>15108254456.342113</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
-      </c>
-      <c r="B38">
-        <v>623022450</v>
-      </c>
-      <c r="C38">
-        <v>1348676594.1699607</v>
-      </c>
-      <c r="D38">
-        <v>1192656505</v>
-      </c>
-      <c r="E38">
-        <v>1657638259.1750178</v>
-      </c>
-      <c r="F38">
-        <v>-27407021.138323274</v>
-      </c>
-    </row>
-    <row r="39"/>
+        <v xml:space="preserve">    Proje Halindeki Yatırım Amaçlı Gayrimenkuller</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">    Maddi Duran Varlıklar</v>
+      </c>
+      <c r="B39">
+        <v>127358461</v>
+      </c>
+      <c r="C39">
+        <v>116947346.37476015</v>
+      </c>
+      <c r="D39">
+        <v>117559584</v>
+      </c>
+      <c r="E39">
+        <v>98727812.38303922</v>
+      </c>
+      <c r="F39">
+        <v>84700331.30983788</v>
+      </c>
+    </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
-      </c>
-      <c r="B40">
-        <v>-514675402</v>
-      </c>
-      <c r="C40">
-        <v>-1210440229.2627501</v>
-      </c>
-      <c r="D40">
-        <v>-618939283</v>
-      </c>
-      <c r="E40">
-        <v>-1145392364.3366659</v>
-      </c>
-      <c r="F40">
-        <v>71242.42340780962</v>
+        <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
-      </c>
-      <c r="B41">
-        <v>-18445348</v>
-      </c>
-      <c r="C41">
-        <v>-68609598.74791612</v>
-      </c>
-      <c r="D41">
-        <v>-51634340</v>
+        <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
-      </c>
-      <c r="B42">
-        <v>-496230054</v>
-      </c>
-      <c r="C42">
-        <v>-1141830630.5148342</v>
-      </c>
-      <c r="D42">
-        <v>-567304943</v>
-      </c>
-      <c r="E42">
-        <v>-1145392364.3366659</v>
-      </c>
-      <c r="F42">
-        <v>71242.42340780962</v>
+        <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
-      </c>
-      <c r="B43">
-        <v>108347048</v>
-      </c>
-      <c r="C43">
-        <v>138236364.90721056</v>
-      </c>
-      <c r="D43">
-        <v>573717222</v>
-      </c>
-      <c r="E43">
-        <v>512245894.838352</v>
-      </c>
-      <c r="F43">
-        <v>-27335778.71491546</v>
+        <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
-      </c>
-    </row>
-    <row r="45"/>
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Duran Varlıklar</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
+      </c>
+    </row>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
-      </c>
-      <c r="B46">
-        <v>108347048</v>
-      </c>
-      <c r="C46">
-        <v>138236364.90721056</v>
-      </c>
-      <c r="D46">
-        <v>573717222</v>
-      </c>
-      <c r="E46">
-        <v>512245894.838352</v>
-      </c>
-      <c r="F46">
-        <v>-27335778.71491546</v>
+        <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">    Azınlık Payları</v>
+        <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>16660847376</v>
+      </c>
+      <c r="C47">
+        <v>16650433969.628033</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>16652700603</v>
+      </c>
+      <c r="E47">
+        <v>16437093489.865484</v>
+      </c>
+      <c r="F47">
+        <v>15192954787.651949</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">    Ana Ortaklık Payları</v>
+        <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>108347048</v>
+        <v>20328021884</v>
       </c>
       <c r="C48">
-        <v>138236364.90721056</v>
+        <v>18607496980.881977</v>
       </c>
       <c r="D48">
-        <v>573717222</v>
+        <v>18368935894</v>
       </c>
       <c r="E48">
-        <v>512245894.838352</v>
+        <v>18020410528.01181</v>
       </c>
       <c r="F48">
-        <v>-27335778.71491546</v>
-      </c>
-    </row>
-    <row r="49"/>
+        <v>16424970942.486774</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Kısa Vadeli Yükümlülükler</v>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">    Amortisman</v>
+        <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>592744</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>2369259.275397212</v>
+        <v>375356150.1180245</v>
       </c>
       <c r="D50">
-        <v>567511</v>
+        <v>447076846</v>
       </c>
       <c r="E50">
-        <v>1907094.122486034</v>
+        <v>877774003.554312</v>
       </c>
       <c r="F50">
-        <v>132135.37751254314</v>
+        <v>199593705.4099583</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    Ticari Borçlar</v>
+      </c>
+      <c r="B52">
+        <v>14998798</v>
+      </c>
+      <c r="C52">
+        <v>29431509.48790713</v>
+      </c>
+      <c r="D52">
+        <v>15721886</v>
+      </c>
+      <c r="E52">
+        <v>42472784.33437493</v>
+      </c>
+      <c r="F52">
+        <v>54810311.84181544</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
+      </c>
+      <c r="B54">
+        <v>4873272</v>
+      </c>
+      <c r="C54">
+        <v>4853388.428073779</v>
+      </c>
+      <c r="D54">
+        <v>1875677</v>
+      </c>
+      <c r="E54">
+        <v>747171.2931639475</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">    Diğer Borçlar</v>
+      </c>
+      <c r="B55">
+        <v>16163651</v>
+      </c>
+      <c r="C55">
+        <v>4226395.838727197</v>
+      </c>
+      <c r="D55">
+        <v>1081733</v>
+      </c>
+      <c r="E55">
+        <v>1058351.8440949724</v>
+      </c>
+      <c r="F55">
+        <v>1232384.498399201</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
+      </c>
+      <c r="B56">
+        <v>5323265</v>
+      </c>
+      <c r="C56">
+        <v>1272423.5877664392</v>
+      </c>
+      <c r="D56">
+        <v>52768483</v>
+      </c>
+      <c r="E56">
+        <v>16001815.39054376</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
+      </c>
+      <c r="B60">
+        <v>11880495</v>
+      </c>
+      <c r="C60">
+        <v>18128531.436773617</v>
+      </c>
+      <c r="D60">
+        <v>23721213</v>
+      </c>
+      <c r="E60">
+        <v>24592681.96081244</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>15744563.928474635</v>
+      </c>
+      <c r="D61">
+        <v>13005751</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
+      </c>
+      <c r="B62">
+        <v>1225117</v>
+      </c>
+      <c r="C62">
+        <v>1229444.865468069</v>
+      </c>
+      <c r="D62">
+        <v>671465</v>
+      </c>
+      <c r="E62">
+        <v>1283461.679917015</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
+      </c>
+      <c r="B63">
+        <v>11481118</v>
+      </c>
+      <c r="C63">
+        <v>1282.0205496102662</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">    Satış Amaçlı Sınıflandırılan Varlık Gruplarına İlişkin Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Varlık Gruplarına İlişkin Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
+      </c>
+      <c r="B66">
+        <v>65945716</v>
+      </c>
+      <c r="C66">
+        <v>450243689.711765</v>
+      </c>
+      <c r="D66">
+        <v>555923054</v>
+      </c>
+      <c r="E66">
+        <v>963930270.0572191</v>
+      </c>
+      <c r="F66">
+        <v>255636401.7501729</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Uzun Vadeli Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">    Finansal Borçlar</v>
+      </c>
+      <c r="F68">
+        <v>1039175180.4295778</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">    Ticari Borçlar</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">    Diğer Borçlar</v>
+      </c>
+      <c r="B73">
+        <v>5123405</v>
+      </c>
+      <c r="C73">
+        <v>4748096.872233458</v>
+      </c>
+      <c r="D73">
+        <v>6659406</v>
+      </c>
+      <c r="E73">
+        <v>3047202.42501857</v>
+      </c>
+      <c r="F73">
+        <v>1870040.2568194044</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve">    Türev Araçlar</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirler</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
+      </c>
+      <c r="B80">
+        <v>6064474</v>
+      </c>
+      <c r="C80">
+        <v>6260842.5959490435</v>
+      </c>
+      <c r="D80">
+        <v>6025516</v>
+      </c>
+      <c r="E80">
+        <v>6948735.302230875</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Borçlar</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
+      </c>
+      <c r="B82">
+        <v>3659720892</v>
+      </c>
+      <c r="C82">
+        <v>3526453397.166756</v>
+      </c>
+      <c r="D82">
+        <v>3296308988</v>
+      </c>
+      <c r="E82">
+        <v>2706303601.554056</v>
+      </c>
+      <c r="F82">
+        <v>1775775966.4445612</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
+      </c>
+      <c r="B84">
+        <v>3670908771</v>
+      </c>
+      <c r="C84">
+        <v>3537462336.6349382</v>
+      </c>
+      <c r="D84">
+        <v>3308993910</v>
+      </c>
+      <c r="E84">
+        <v>2716299539.281306</v>
+      </c>
+      <c r="F84">
+        <v>2816821187.1309586</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Özkaynaklar</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
+      </c>
+      <c r="B86">
+        <v>16591167397</v>
+      </c>
+      <c r="C86">
+        <v>14619790954.535273</v>
+      </c>
+      <c r="D86">
+        <v>14504018930</v>
+      </c>
+      <c r="E86">
+        <v>14340180718.673285</v>
+      </c>
+      <c r="F86">
+        <v>13352513353.605642</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve">    Ödenmiş Sermaye</v>
+      </c>
+      <c r="B87">
+        <v>701000000</v>
+      </c>
+      <c r="C87">
+        <v>595348000</v>
+      </c>
+      <c r="D87">
+        <v>595348000</v>
+      </c>
+      <c r="E87">
+        <v>595348000</v>
+      </c>
+      <c r="F87">
+        <v>210971707</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
+      </c>
+      <c r="B88">
+        <v>551662643</v>
+      </c>
+      <c r="C88">
+        <v>548791908.3334413</v>
+      </c>
+      <c r="D88">
+        <v>548791908</v>
+      </c>
+      <c r="E88">
+        <v>548791908.3453887</v>
+      </c>
+      <c r="F88">
+        <v>258532190.2073868</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">    Birleşme Denkleştirme Hesabı</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve">    Sermaye Avansı</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve">    Karşılıklı İştirak Sermaye Düzeltmesi (-)</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
+      </c>
+      <c r="B94">
+        <v>2070724296</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">    Ortak Kontrole Tabi Teşebbüs veya İşletmeleri İçeren Birleşmelerin Etkisi</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">    Pay Bazlı Ödemeler (-)</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
+      </c>
+      <c r="B97">
+        <v>26801020</v>
+      </c>
+      <c r="C97">
+        <v>26581052.37032229</v>
+      </c>
+      <c r="D97">
+        <v>26754890</v>
+      </c>
+      <c r="E97">
+        <v>10848111.995568989</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
+      </c>
+      <c r="B99">
+        <v>47607068</v>
+      </c>
+      <c r="C99">
+        <v>47607065.82368869</v>
+      </c>
+      <c r="D99">
+        <v>13542320</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v xml:space="preserve">    Diğer Özkaynak Payları</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Diğer Yedekler</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">    Ödenen Kar Payı Avansları (Net) (-)</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
+      </c>
+      <c r="B103">
+        <v>12932237347</v>
+      </c>
+      <c r="C103">
+        <v>13285517066.550716</v>
+      </c>
+      <c r="D103">
+        <v>13171650377</v>
+      </c>
+      <c r="E103">
+        <v>12637020942.375511</v>
+      </c>
+      <c r="F103">
+        <v>12912262403.019392</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
+      </c>
+      <c r="B104">
+        <v>261135023</v>
+      </c>
+      <c r="C104">
+        <v>115945861.45710342</v>
+      </c>
+      <c r="D104">
+        <v>147931435</v>
+      </c>
+      <c r="E104">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="F104">
+        <v>-29252946.621135674</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve">    Azınlık Payları</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve">    Toplam Özkaynaklar</v>
+      </c>
+      <c r="B106">
+        <v>16591167397</v>
+      </c>
+      <c r="C106">
+        <v>14619790954.535273</v>
+      </c>
+      <c r="D106">
+        <v>14504018930</v>
+      </c>
+      <c r="E106">
+        <v>14340180718.673285</v>
+      </c>
+      <c r="F106">
+        <v>13352513353.605642</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v xml:space="preserve">    Toplam Kaynaklar</v>
+      </c>
+      <c r="B107">
+        <v>20328021884</v>
+      </c>
+      <c r="C107">
+        <v>18607496980.881977</v>
+      </c>
+      <c r="D107">
+        <v>18368935894</v>
+      </c>
+      <c r="E107">
+        <v>18020410528.01181</v>
+      </c>
+      <c r="F107">
+        <v>16424970942.486774</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
+      </c>
+      <c r="C108">
+        <v>-378238347.4104854</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:H50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1943,6 +1498,8 @@
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1950,18 +1507,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1975,10 +1538,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>360563785</v>
+        <v>574785159</v>
+      </c>
+      <c r="C3">
+        <v>385851571</v>
       </c>
       <c r="D3">
-        <v>717521685</v>
+        <v>1532960726.2467282</v>
+      </c>
+      <c r="E3">
+        <v>873424074</v>
+      </c>
+      <c r="F3">
+        <v>767844361</v>
+      </c>
+      <c r="G3">
+        <v>808382819.1590298</v>
+      </c>
+      <c r="H3">
+        <v>7181353.509643215</v>
       </c>
     </row>
     <row r="4">
@@ -2001,10 +1579,22 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-23483744</v>
+        <v>-37368895</v>
+      </c>
+      <c r="C7">
+        <v>-25130753</v>
       </c>
       <c r="D7">
-        <v>-310048709</v>
+        <v>-554198576.0417489</v>
+      </c>
+      <c r="E7">
+        <v>-340122533</v>
+      </c>
+      <c r="F7">
+        <v>-331793670</v>
+      </c>
+      <c r="G7">
+        <v>-286623550.2216531</v>
       </c>
     </row>
     <row r="8">
@@ -2012,10 +1602,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>337080041</v>
+        <v>537416264</v>
+      </c>
+      <c r="C8">
+        <v>360720818</v>
       </c>
       <c r="D8">
-        <v>407472976</v>
+        <v>978762150.2049793</v>
+      </c>
+      <c r="E8">
+        <v>533301541</v>
+      </c>
+      <c r="F8">
+        <v>436050691</v>
+      </c>
+      <c r="G8">
+        <v>521759268.9373768</v>
+      </c>
+      <c r="H8">
+        <v>7181353.509643215</v>
       </c>
     </row>
     <row r="9">
@@ -2043,10 +1648,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>337080041</v>
+        <v>537416264</v>
+      </c>
+      <c r="C13">
+        <v>360720818</v>
       </c>
       <c r="D13">
-        <v>407472976</v>
+        <v>978762150.2049793</v>
+      </c>
+      <c r="E13">
+        <v>533301541</v>
+      </c>
+      <c r="F13">
+        <v>436050691</v>
+      </c>
+      <c r="G13">
+        <v>521759268.9373768</v>
+      </c>
+      <c r="H13">
+        <v>7181353.509643215</v>
       </c>
     </row>
     <row r="14"/>
@@ -2055,10 +1675,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-35274297</v>
+        <v>-95825992</v>
+      </c>
+      <c r="C15">
+        <v>-37748225</v>
       </c>
       <c r="D15">
-        <v>-39012411</v>
+        <v>-147873520.6564045</v>
+      </c>
+      <c r="E15">
+        <v>-90602269</v>
+      </c>
+      <c r="F15">
+        <v>-41748508</v>
+      </c>
+      <c r="G15">
+        <v>-142943157.1658684</v>
+      </c>
+      <c r="H15">
+        <v>-3835362.408575161</v>
       </c>
     </row>
     <row r="16">
@@ -2066,10 +1701,22 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-1125701</v>
+        <v>-3360226</v>
+      </c>
+      <c r="C16">
+        <v>-1204651</v>
       </c>
       <c r="D16">
-        <v>-365307</v>
+        <v>-5735227.716722589</v>
+      </c>
+      <c r="E16">
+        <v>-1545765</v>
+      </c>
+      <c r="F16">
+        <v>-390927</v>
+      </c>
+      <c r="G16">
+        <v>-11667802.19388879</v>
       </c>
     </row>
     <row r="17">
@@ -2082,10 +1729,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>10141665</v>
+        <v>14970001</v>
+      </c>
+      <c r="C18">
+        <v>10852941</v>
       </c>
       <c r="D18">
-        <v>7318603</v>
+        <v>10967567.643956665</v>
+      </c>
+      <c r="E18">
+        <v>11675714</v>
+      </c>
+      <c r="F18">
+        <v>7831886</v>
+      </c>
+      <c r="G18">
+        <v>2542976.8830007943</v>
       </c>
     </row>
     <row r="19">
@@ -2093,10 +1752,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-1888316</v>
+        <v>-7454029</v>
+      </c>
+      <c r="C19">
+        <v>-2020751</v>
       </c>
       <c r="D19">
-        <v>-60887965</v>
+        <v>-27953878.22091028</v>
+      </c>
+      <c r="E19">
+        <v>-78308975</v>
+      </c>
+      <c r="F19">
+        <v>-65158282</v>
+      </c>
+      <c r="G19">
+        <v>-5091265.915349743</v>
       </c>
     </row>
     <row r="20">
@@ -2109,10 +1780,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>308933392</v>
+        <v>445746018</v>
+      </c>
+      <c r="C21">
+        <v>330600132</v>
       </c>
       <c r="D21">
-        <v>314525896</v>
+        <v>808167091.2548985</v>
+      </c>
+      <c r="E21">
+        <v>374520246</v>
+      </c>
+      <c r="F21">
+        <v>336584860</v>
+      </c>
+      <c r="G21">
+        <v>364600020.5452707</v>
+      </c>
+      <c r="H21">
+        <v>3345991.101068054</v>
       </c>
     </row>
     <row r="22"/>
@@ -2131,10 +1817,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
+        <v>3743276</v>
+      </c>
+      <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>684518774</v>
+        <v>950947222.7848526</v>
+      </c>
+      <c r="E25">
+        <v>732526826</v>
+      </c>
+      <c r="F25">
+        <v>732526826</v>
+      </c>
+      <c r="G25">
+        <v>759529089.5063648</v>
       </c>
     </row>
     <row r="26">
@@ -2144,8 +1842,20 @@
       <c r="B26">
         <v>0</v>
       </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
       <c r="D26">
-        <v>-31974282</v>
+        <v>-859578275.1933765</v>
+      </c>
+      <c r="E26">
+        <v>-34216767</v>
+      </c>
+      <c r="F26">
+        <v>-34216767</v>
+      </c>
+      <c r="G26">
+        <v>-126198466.36352229</v>
       </c>
     </row>
     <row r="27">
@@ -2183,10 +1893,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>308933392</v>
+        <v>449489294</v>
+      </c>
+      <c r="C33">
+        <v>330600132</v>
       </c>
       <c r="D33">
-        <v>967070388</v>
+        <v>899536038.8463746</v>
+      </c>
+      <c r="E33">
+        <v>1072830305</v>
+      </c>
+      <c r="F33">
+        <v>1034894919</v>
+      </c>
+      <c r="G33">
+        <v>997930643.6881132</v>
+      </c>
+      <c r="H33">
+        <v>3345991.101068054</v>
       </c>
     </row>
     <row r="34"/>
@@ -2195,10 +1920,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>22092456</v>
+        <v>232185896</v>
+      </c>
+      <c r="C35">
+        <v>23641889</v>
       </c>
       <c r="D35">
-        <v>857856</v>
+        <v>13016214.349819433</v>
+      </c>
+      <c r="E35">
+        <v>3366715</v>
+      </c>
+      <c r="F35">
+        <v>918021</v>
+      </c>
+      <c r="G35">
+        <v>4960256.842609432</v>
       </c>
     </row>
     <row r="36">
@@ -2206,10 +1943,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-6830472</v>
+        <v>-27042566</v>
+      </c>
+      <c r="C36">
+        <v>-7309520</v>
       </c>
       <c r="D36">
-        <v>-74081442</v>
+        <v>-241318034.8681966</v>
+      </c>
+      <c r="E36">
+        <v>-176996553</v>
+      </c>
+      <c r="F36">
+        <v>-79277071</v>
+      </c>
+      <c r="G36">
+        <v>-177964463.25320804</v>
+      </c>
+      <c r="H36">
+        <v>-32675176.662782066</v>
       </c>
     </row>
     <row r="37">
@@ -2217,10 +1969,22 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>298827074</v>
+        <v>493811428</v>
+      </c>
+      <c r="C37">
+        <v>319785016</v>
       </c>
       <c r="D37">
-        <v>298809703</v>
+        <v>772030479.9226495</v>
+      </c>
+      <c r="E37">
+        <v>491743066</v>
+      </c>
+      <c r="F37">
+        <v>319766427</v>
+      </c>
+      <c r="G37">
+        <v>948968647.9333044</v>
       </c>
     </row>
     <row r="38">
@@ -2228,10 +1992,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>623022450</v>
+        <v>1148444052</v>
+      </c>
+      <c r="C38">
+        <v>666717517</v>
       </c>
       <c r="D38">
-        <v>1192656505</v>
+        <v>1443264698.2506468</v>
+      </c>
+      <c r="E38">
+        <v>1390943533</v>
+      </c>
+      <c r="F38">
+        <v>1276302296</v>
+      </c>
+      <c r="G38">
+        <v>1773895085.210819</v>
+      </c>
+      <c r="H38">
+        <v>-29329185.561714012</v>
       </c>
     </row>
     <row r="39"/>
@@ -2240,10 +2019,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-514675402</v>
+        <v>-887309029</v>
+      </c>
+      <c r="C40">
+        <v>-550771654</v>
       </c>
       <c r="D40">
-        <v>-618939283</v>
+        <v>-1295333262.094998</v>
+      </c>
+      <c r="E40">
+        <v>-939551663</v>
+      </c>
+      <c r="F40">
+        <v>-662347980</v>
+      </c>
+      <c r="G40">
+        <v>-1225723329.254002</v>
+      </c>
+      <c r="H40">
+        <v>76238.94057833671</v>
       </c>
     </row>
     <row r="41">
@@ -2251,10 +2045,19 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-18445348</v>
+        <v>-26785579</v>
+      </c>
+      <c r="C41">
+        <v>-19738994</v>
       </c>
       <c r="D41">
-        <v>-51634340</v>
+        <v>-73421465.35504445</v>
+      </c>
+      <c r="E41">
+        <v>-44455321</v>
+      </c>
+      <c r="F41">
+        <v>-55255664</v>
       </c>
     </row>
     <row r="42">
@@ -2262,10 +2065,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-496230054</v>
+        <v>-860523450</v>
+      </c>
+      <c r="C42">
+        <v>-531032660</v>
       </c>
       <c r="D42">
-        <v>-567304943</v>
+        <v>-1221911796.7399538</v>
+      </c>
+      <c r="E42">
+        <v>-895096342</v>
+      </c>
+      <c r="F42">
+        <v>-607092316</v>
+      </c>
+      <c r="G42">
+        <v>-1225723329.254002</v>
+      </c>
+      <c r="H42">
+        <v>76238.94057833671</v>
       </c>
     </row>
     <row r="43">
@@ -2273,10 +2091,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>108347048</v>
+        <v>261135023</v>
+      </c>
+      <c r="C43">
+        <v>115945863</v>
       </c>
       <c r="D43">
-        <v>573717222</v>
+        <v>147931436.15564892</v>
+      </c>
+      <c r="E43">
+        <v>451391870</v>
+      </c>
+      <c r="F43">
+        <v>613954316</v>
+      </c>
+      <c r="G43">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="H43">
+        <v>-29252946.621135674</v>
       </c>
     </row>
     <row r="44">
@@ -2290,10 +2123,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>108347048</v>
+        <v>261135023</v>
+      </c>
+      <c r="C46">
+        <v>115945863</v>
       </c>
       <c r="D46">
-        <v>573717222</v>
+        <v>147931436.15564892</v>
+      </c>
+      <c r="E46">
+        <v>451391870</v>
+      </c>
+      <c r="F46">
+        <v>613954316</v>
+      </c>
+      <c r="G46">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="H46">
+        <v>-29252946.621135674</v>
       </c>
     </row>
     <row r="47">
@@ -2303,7 +2151,13 @@
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="D47">
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>0</v>
       </c>
     </row>
@@ -2312,10 +2166,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>108347048</v>
+        <v>261135023</v>
+      </c>
+      <c r="C48">
+        <v>115945863</v>
       </c>
       <c r="D48">
-        <v>573717222</v>
+        <v>147931436.15564892</v>
+      </c>
+      <c r="E48">
+        <v>451391870</v>
+      </c>
+      <c r="F48">
+        <v>613954316</v>
+      </c>
+      <c r="G48">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="H48">
+        <v>-29252946.621135674</v>
       </c>
     </row>
     <row r="49"/>
@@ -2324,22 +2193,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>592744</v>
+        <v>1655951</v>
+      </c>
+      <c r="C50">
+        <v>634315.5164091716</v>
       </c>
       <c r="D50">
-        <v>567511</v>
+        <v>2535424.940245371</v>
+      </c>
+      <c r="E50">
+        <v>654219</v>
+      </c>
+      <c r="F50">
+        <v>607312.8248162536</v>
+      </c>
+      <c r="G50">
+        <v>2040846.2897062215</v>
+      </c>
+      <c r="H50">
+        <v>141402.56202136108</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:H50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2347,6 +2231,8 @@
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2354,18 +2240,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2379,16 +2271,16 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1075536259.7869642</v>
+        <v>188933588</v>
       </c>
       <c r="C3">
-        <v>1432494159.7869642</v>
+        <v>385851571</v>
       </c>
       <c r="E3">
-        <v>755403349.5382925</v>
+        <v>105579713</v>
       </c>
       <c r="F3">
-        <v>6710704.837896678</v>
+        <v>767844361</v>
       </c>
     </row>
     <row r="4">
@@ -2411,13 +2303,16 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-231312766.60098696</v>
+        <v>-12238142</v>
       </c>
       <c r="C7">
-        <v>-517877731.60098696</v>
+        <v>-25130753</v>
       </c>
       <c r="E7">
-        <v>-267838930.71755072</v>
+        <v>-8328863</v>
+      </c>
+      <c r="F7">
+        <v>-331793670</v>
       </c>
     </row>
     <row r="8">
@@ -2425,16 +2320,16 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>844223493.1859773</v>
+        <v>176695446</v>
       </c>
       <c r="C8">
-        <v>914616428.1859773</v>
+        <v>360720818</v>
       </c>
       <c r="E8">
-        <v>487564418.8207418</v>
+        <v>97250850</v>
       </c>
       <c r="F8">
-        <v>6710704.837896678</v>
+        <v>436050691</v>
       </c>
     </row>
     <row r="9">
@@ -2462,16 +2357,16 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>844223493.1859773</v>
+        <v>176695446</v>
       </c>
       <c r="C13">
-        <v>914616428.1859773</v>
+        <v>360720818</v>
       </c>
       <c r="E13">
-        <v>487564418.8207418</v>
+        <v>97250850</v>
       </c>
       <c r="F13">
-        <v>6710704.837896678</v>
+        <v>436050691</v>
       </c>
     </row>
     <row r="14"/>
@@ -2480,16 +2375,16 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-134444131.05077308</v>
+        <v>-58077767</v>
       </c>
       <c r="C15">
-        <v>-138182245.05077308</v>
+        <v>-37748225</v>
       </c>
       <c r="E15">
-        <v>-133575005.74914268</v>
+        <v>-48853761</v>
       </c>
       <c r="F15">
-        <v>-3584001.9622695204</v>
+        <v>-41748508</v>
       </c>
     </row>
     <row r="16">
@@ -2497,13 +2392,16 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-6119748.658333974</v>
+        <v>-2155575</v>
       </c>
       <c r="C16">
-        <v>-5359354.658333974</v>
+        <v>-1204651</v>
       </c>
       <c r="E16">
-        <v>-10903122.444120016</v>
+        <v>-1154838</v>
+      </c>
+      <c r="F16">
+        <v>-390927</v>
       </c>
     </row>
     <row r="17">
@@ -2516,13 +2414,16 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>13071841.585829869</v>
+        <v>4117060</v>
       </c>
       <c r="C18">
-        <v>10248779.585829869</v>
+        <v>10852941</v>
       </c>
       <c r="E18">
-        <v>2376316.281951239</v>
+        <v>3843828</v>
+      </c>
+      <c r="F18">
+        <v>7831886</v>
       </c>
     </row>
     <row r="19">
@@ -2530,13 +2431,16 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>32877800.86049</v>
+        <v>-5433278</v>
       </c>
       <c r="C19">
-        <v>-26121848.13951</v>
+        <v>-2020751</v>
       </c>
       <c r="E19">
-        <v>-4757596.567733012</v>
+        <v>-13150693</v>
+      </c>
+      <c r="F19">
+        <v>-65158282</v>
       </c>
     </row>
     <row r="20">
@@ -2549,16 +2453,16 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>749609255.9231901</v>
+        <v>115145886</v>
       </c>
       <c r="C21">
-        <v>755201759.9231901</v>
+        <v>330600132</v>
       </c>
       <c r="E21">
-        <v>340705010.34169734</v>
+        <v>37935386</v>
       </c>
       <c r="F21">
-        <v>3126702.8756271577</v>
+        <v>336584860</v>
       </c>
     </row>
     <row r="22"/>
@@ -2577,13 +2481,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>204105650.34528875</v>
+        <v>3743276</v>
       </c>
       <c r="C25">
-        <v>888624424.3452888</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>709751376.0643222</v>
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>732526826</v>
       </c>
     </row>
     <row r="26">
@@ -2591,13 +2498,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-771269296.2676934</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>-803243578.2676934</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>-117927721.78999792</v>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>-34216767</v>
       </c>
     </row>
     <row r="27">
@@ -2635,16 +2545,16 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>182445610.00078547</v>
+        <v>118889162</v>
       </c>
       <c r="C33">
-        <v>840582606.0007855</v>
+        <v>330600132</v>
       </c>
       <c r="E33">
-        <v>932528664.6160216</v>
+        <v>37935386</v>
       </c>
       <c r="F33">
-        <v>3126702.8756271577</v>
+        <v>1034894919</v>
       </c>
     </row>
     <row r="34"/>
@@ -2653,13 +2563,16 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>33397762.903920747</v>
+        <v>208544007</v>
       </c>
       <c r="C35">
-        <v>12163162.90392075</v>
+        <v>23641889</v>
       </c>
       <c r="E35">
-        <v>4635173.515161347</v>
+        <v>2448694</v>
+      </c>
+      <c r="F35">
+        <v>918021</v>
       </c>
     </row>
     <row r="36">
@@ -2667,16 +2580,16 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-158251660.09433472</v>
+        <v>-19733046</v>
       </c>
       <c r="C36">
-        <v>-225502630.09433472</v>
+        <v>-7309520</v>
       </c>
       <c r="E36">
-        <v>-166301099.496538</v>
+        <v>-97719482</v>
       </c>
       <c r="F36">
-        <v>-30533724.01395043</v>
+        <v>-79277071</v>
       </c>
     </row>
     <row r="37">
@@ -2684,13 +2597,16 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>721450826.3595893</v>
+        <v>174026412</v>
       </c>
       <c r="C37">
-        <v>721433455.3595893</v>
+        <v>319785016</v>
       </c>
       <c r="E37">
-        <v>886775520.5403728</v>
+        <v>171976639</v>
+      </c>
+      <c r="F37">
+        <v>319766427</v>
       </c>
     </row>
     <row r="38">
@@ -2698,16 +2614,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>779042539.1699607</v>
+        <v>481726535</v>
       </c>
       <c r="C38">
-        <v>1348676594.1699607</v>
+        <v>666717517</v>
       </c>
       <c r="E38">
-        <v>1657638259.1750178</v>
+        <v>114641237</v>
       </c>
       <c r="F38">
-        <v>-27407021.138323274</v>
+        <v>1276302296</v>
       </c>
     </row>
     <row r="39"/>
@@ -2716,16 +2632,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-1106176348.2627501</v>
+        <v>-336537375</v>
       </c>
       <c r="C40">
-        <v>-1210440229.2627501</v>
+        <v>-550771654</v>
       </c>
       <c r="E40">
-        <v>-1145392364.3366659</v>
+        <v>-277203683</v>
       </c>
       <c r="F40">
-        <v>71242.42340780962</v>
+        <v>-662347980</v>
       </c>
     </row>
     <row r="41">
@@ -2733,10 +2649,16 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-35420606.74791612</v>
+        <v>-7046585</v>
       </c>
       <c r="C41">
-        <v>-68609598.74791612</v>
+        <v>-19738994</v>
+      </c>
+      <c r="E41">
+        <v>10800343</v>
+      </c>
+      <c r="F41">
+        <v>-55255664</v>
       </c>
     </row>
     <row r="42">
@@ -2744,16 +2666,16 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-1070755741.5148342</v>
+        <v>-329490790</v>
       </c>
       <c r="C42">
-        <v>-1141830630.5148342</v>
+        <v>-531032660</v>
       </c>
       <c r="E42">
-        <v>-1145392364.3366659</v>
+        <v>-288004026</v>
       </c>
       <c r="F42">
-        <v>71242.42340780962</v>
+        <v>-607092316</v>
       </c>
     </row>
     <row r="43">
@@ -2761,16 +2683,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-327133809.0927894</v>
+        <v>145189160</v>
       </c>
       <c r="C43">
-        <v>138236364.90721056</v>
+        <v>115945863</v>
       </c>
       <c r="E43">
-        <v>512245894.838352</v>
+        <v>-162562446</v>
       </c>
       <c r="F43">
-        <v>-27335778.71491546</v>
+        <v>613954316</v>
       </c>
     </row>
     <row r="44">
@@ -2784,38 +2706,50 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-327133809.0927894</v>
+        <v>145189160</v>
       </c>
       <c r="C46">
-        <v>138236364.90721056</v>
+        <v>115945863</v>
       </c>
       <c r="E46">
-        <v>512245894.838352</v>
+        <v>-162562446</v>
       </c>
       <c r="F46">
-        <v>-27335778.71491546</v>
+        <v>613954316</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-327133809.0927894</v>
+        <v>145189160</v>
       </c>
       <c r="C48">
-        <v>138236364.90721056</v>
+        <v>115945863</v>
       </c>
       <c r="E48">
-        <v>512245894.838352</v>
+        <v>-162562446</v>
       </c>
       <c r="F48">
-        <v>-27335778.71491546</v>
+        <v>613954316</v>
       </c>
     </row>
     <row r="49"/>
@@ -2824,28 +2758,28 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>2394492.275397212</v>
+        <v>1021635.4835908284</v>
       </c>
       <c r="C50">
-        <v>2369259.275397212</v>
+        <v>634315.5164091716</v>
       </c>
       <c r="E50">
-        <v>1907094.122486034</v>
+        <v>46906.17518374638</v>
       </c>
       <c r="F50">
-        <v>132135.37751254314</v>
+        <v>607312.8248162536</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:H50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2853,6 +2787,8 @@
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2860,18 +2796,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2882,1097 +2824,545 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
+        <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>416438534</v>
+        <v>1234321811.2467282</v>
       </c>
       <c r="C3">
-        <v>80977529.285796</v>
+        <v>1150967936.2467282</v>
       </c>
       <c r="D3">
-        <v>-171487473</v>
-      </c>
-      <c r="E3">
-        <v>465204896.0353741</v>
-      </c>
-      <c r="F3">
-        <v>531596.2816381938</v>
+        <v>1532960726.2467282</v>
+      </c>
+      <c r="G3">
+        <v>808382819.1590298</v>
+      </c>
+      <c r="H3">
+        <v>7181353.509643215</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
-      </c>
-      <c r="B4">
-        <v>108347048</v>
-      </c>
-      <c r="C4">
-        <v>138236364.90721056</v>
-      </c>
-      <c r="D4">
-        <v>573717222</v>
-      </c>
-      <c r="E4">
-        <v>512245894.838352</v>
-      </c>
-      <c r="F4">
-        <v>-27335778.71491546</v>
+        <v xml:space="preserve">    Toplam Hasılat</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B5">
-        <v>79849594</v>
-      </c>
-      <c r="C5">
-        <v>46657546.83871628</v>
-      </c>
-      <c r="D5">
-        <v>-551117869</v>
-      </c>
-      <c r="E5">
-        <v>-109277071.93040152</v>
-      </c>
-      <c r="F5">
-        <v>30955365.02475049</v>
+        <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B6">
-        <v>592744</v>
-      </c>
-      <c r="C6">
-        <v>2369259.275397212</v>
-      </c>
-      <c r="D6">
-        <v>567511</v>
-      </c>
-      <c r="E6">
-        <v>1907094.122486034</v>
-      </c>
-      <c r="F6">
-        <v>132135.37751254314</v>
+        <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>234705</v>
+        <v>-251444938.04174888</v>
       </c>
       <c r="C7">
-        <v>5613198.914513058</v>
+        <v>-247535659.04174888</v>
       </c>
       <c r="D7">
-        <v>56503</v>
-      </c>
-      <c r="E7">
-        <v>1563171.5188097453</v>
+        <v>-554198576.0417489</v>
+      </c>
+      <c r="G7">
+        <v>-286623550.2216531</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>-198514</v>
+        <v>982876873.2049793</v>
       </c>
       <c r="C8">
-        <v>-166748.0524151434</v>
+        <v>903432277.2049793</v>
       </c>
       <c r="D8">
-        <v>887983</v>
-      </c>
-      <c r="E8">
-        <v>6738314.426925299</v>
-      </c>
-      <c r="F8">
-        <v>954363.0241870075</v>
+        <v>978762150.2049793</v>
+      </c>
+      <c r="G8">
+        <v>521759268.9373768</v>
+      </c>
+      <c r="H8">
+        <v>7181353.509643215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">    Kar Payı (Geliri) Gideri ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan (Gelirler) Giderler ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">    Pazarlıklı Satın Alım Sonucu Oluşan Kazanç ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B12">
-        <v>-27667338</v>
-      </c>
-      <c r="C12">
-        <v>37844259.003030844</v>
-      </c>
-      <c r="D12">
-        <v>55521980</v>
-      </c>
-      <c r="E12">
-        <v>62467278.40093686</v>
-      </c>
-      <c r="F12">
-        <v>645466.8541010339</v>
+        <v xml:space="preserve">    Canlı Varlıklar Gerçeğe Uygun Değer Farkları</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Gelirler ile İlgili Düzeltmeler</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v xml:space="preserve">    Takas İşlemlerinden Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Brüt Kar (Zarar)</v>
+      </c>
+      <c r="B13">
+        <v>982876873.2049793</v>
+      </c>
+      <c r="C13">
+        <v>903432277.2049793</v>
+      </c>
+      <c r="D13">
+        <v>978762150.2049793</v>
+      </c>
+      <c r="G13">
+        <v>521759268.9373768</v>
+      </c>
+      <c r="H13">
+        <v>7181353.509643215</v>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>5143865</v>
+        <v>-153097243.6564045</v>
       </c>
       <c r="C15">
-        <v>163799599.20311224</v>
+        <v>-143873237.6564045</v>
       </c>
       <c r="D15">
-        <v>72388067</v>
-      </c>
-      <c r="E15">
-        <v>86865997.67364188</v>
-      </c>
-      <c r="F15">
-        <v>29082521.538315304</v>
+        <v>-147873520.6564045</v>
+      </c>
+      <c r="G15">
+        <v>-142943157.1658684</v>
+      </c>
+      <c r="H15">
+        <v>-3835362.408575161</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">    Pay Bazlı Ödemeler İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
+      </c>
+      <c r="B16">
+        <v>-7549688.716722589</v>
+      </c>
+      <c r="C16">
+        <v>-6548951.716722589</v>
+      </c>
+      <c r="D16">
+        <v>-5735227.716722589</v>
+      </c>
+      <c r="G16">
+        <v>-11667802.19388879</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">    Hibe Krediler ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>14261854.643956665</v>
       </c>
       <c r="C18">
-        <v>-74747776.00590801</v>
+        <v>13988622.643956665</v>
       </c>
       <c r="D18">
-        <v>-641911422</v>
-      </c>
-      <c r="E18">
-        <v>-591823654.2743243</v>
+        <v>10967567.643956665</v>
+      </c>
+      <c r="G18">
+        <v>2542976.8830007943</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
+      </c>
+      <c r="B19">
+        <v>42901067.77908972</v>
+      </c>
+      <c r="C19">
+        <v>35183652.77908972</v>
+      </c>
+      <c r="D19">
+        <v>-27953878.22091028</v>
+      </c>
+      <c r="G19">
+        <v>-5091265.915349743</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B20">
-        <v>514675402</v>
-      </c>
-      <c r="C20">
-        <v>1210440229.2627501</v>
-      </c>
-      <c r="D20">
-        <v>618939283</v>
-      </c>
-      <c r="E20">
-        <v>1145392364.3366659</v>
-      </c>
-      <c r="F20">
-        <v>-71242.42340780962</v>
+        <v xml:space="preserve">    Diğer Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
+        <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
+      </c>
+      <c r="B21">
+        <v>879392863.2548985</v>
       </c>
       <c r="C21">
-        <v>-750913416.3267394</v>
-      </c>
-      <c r="E21">
-        <v>-850691283.1535202</v>
-      </c>
-      <c r="F21">
-        <v>212120.6540424091</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>-547581058.4350246</v>
-      </c>
-      <c r="D22">
-        <v>-345414094</v>
-      </c>
-      <c r="E22">
-        <v>28303645.01797733</v>
-      </c>
-    </row>
+        <v>802182363.2548985</v>
+      </c>
+      <c r="D21">
+        <v>808167091.2548985</v>
+      </c>
+      <c r="G21">
+        <v>364600020.5452707</v>
+      </c>
+      <c r="H21">
+        <v>3345991.101068054</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Ödenecek Kar Paylarının Defter Değeri ile Dağıtılan Nakit Dışı Varlıkların Değeri Arasındaki Fark</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">    İştirak, İş ortaklığı ve Finansal Yatırımların Elden Çıkarılmasından veya Paylarındaki Değişim Sebebi ile Oluşan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Finansal Tablo Dışı Bırakılmasından Kaynaklanan Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların veya Müşterek Faaliyetlerin Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
+      </c>
+      <c r="B25">
+        <v>222163672.78485262</v>
+      </c>
+      <c r="C25">
+        <v>218420396.78485262</v>
+      </c>
+      <c r="D25">
+        <v>950947222.7848526</v>
+      </c>
+      <c r="G25">
+        <v>759529089.5063648</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
+      </c>
+      <c r="B26">
+        <v>-825361508.1933765</v>
+      </c>
+      <c r="C26">
+        <v>-825361508.1933765</v>
+      </c>
+      <c r="D26">
+        <v>-859578275.1933765</v>
+      </c>
+      <c r="G26">
+        <v>-126198466.36352229</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
+        <v xml:space="preserve">    TFRS 9 Uyarınca Belirlenen Değer Düşüklüğü Kazançları (Zararları) ve Değer Düşüklüğü Zararlarının İptalleri</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
-      </c>
-      <c r="B28">
-        <v>244127923</v>
-      </c>
-      <c r="C28">
-        <v>-103916382.46013086</v>
-      </c>
-      <c r="D28">
-        <v>-194392770</v>
-      </c>
-      <c r="E28">
-        <v>62236073.12742361</v>
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
+        <v xml:space="preserve">    İştirakler, Müşterek Kontrol Edilen İşletmeler ve Bağlı Ortaklıklardan Diğer Gelirler (Giderler)</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabındaki Azalış (Artış)</v>
+        <v xml:space="preserve">    İtfa Edilmiş Maliyetinden Ölçülen Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
-      </c>
-      <c r="B31">
-        <v>155632921</v>
-      </c>
-      <c r="C31">
-        <v>-152143296.1937522</v>
-      </c>
-      <c r="D31">
-        <v>-275495861</v>
-      </c>
-      <c r="E31">
-        <v>-29603564.77257269</v>
-      </c>
-      <c r="F31">
-        <v>-6710704.837896678</v>
+        <v xml:space="preserve">    Gerçeğe Uygun Değer Farkı Diğer Kapsamlı Gelire Yansıtılan Finansal Varlıkların Gerçeğe Uygun Değer Farkı Kar veya Zarara Yansıtılan Olarak Sınıflandırılmasından Kazançlar (Kayıplar)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
+        <v xml:space="preserve">    Risk Pozisyonlarını Netleştiren Kalemler Grubuna Yönelik Finansal Riskten Korunma Kazançları (Kayıpları)</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>-525081</v>
+        <v>276195027.84637463</v>
       </c>
       <c r="C33">
-        <v>-1004691.926690515</v>
+        <v>195241251.84637463</v>
       </c>
       <c r="D33">
-        <v>-333014</v>
-      </c>
-      <c r="E33">
-        <v>-49512.3893484961</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
-      </c>
-    </row>
+        <v>899536038.8463746</v>
+      </c>
+      <c r="G33">
+        <v>997930643.6881132</v>
+      </c>
+      <c r="H33">
+        <v>3345991.101068054</v>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklardaki Azalış (Artış)</v>
+        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
+      </c>
+      <c r="B35">
+        <v>241835395.34981942</v>
+      </c>
+      <c r="C35">
+        <v>35740082.34981944</v>
+      </c>
+      <c r="D35">
+        <v>13016214.349819433</v>
+      </c>
+      <c r="G35">
+        <v>4960256.842609432</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
+        <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
+      </c>
+      <c r="B36">
+        <v>-91364047.8681966</v>
+      </c>
+      <c r="C36">
+        <v>-169350483.8681966</v>
+      </c>
+      <c r="D36">
+        <v>-241318034.8681966</v>
+      </c>
+      <c r="G36">
+        <v>-177964463.25320804</v>
+      </c>
+      <c r="H36">
+        <v>-32675176.662782066</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>40173899</v>
+        <v>774098841.9226495</v>
       </c>
       <c r="C37">
-        <v>49487403.16561512</v>
+        <v>772049068.9226495</v>
       </c>
       <c r="D37">
-        <v>3361629</v>
-      </c>
-      <c r="E37">
-        <v>72325047.22350001</v>
+        <v>772030479.9226495</v>
+      </c>
+      <c r="G37">
+        <v>948968647.9333044</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">    Canlı Varlıklardaki Azalış (Artış)</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
-      </c>
-      <c r="B39">
-        <v>-18738792</v>
-      </c>
-      <c r="C39">
-        <v>-461871.3402260186</v>
-      </c>
-      <c r="D39">
-        <v>-2290321</v>
-      </c>
-      <c r="E39">
-        <v>-3586909.277303941</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
+      </c>
+      <c r="B38">
+        <v>1200765217.2506468</v>
+      </c>
+      <c r="C38">
+        <v>833679919.2506468</v>
+      </c>
+      <c r="D38">
+        <v>1443264698.2506468</v>
+      </c>
+      <c r="G38">
+        <v>1773895085.210819</v>
+      </c>
+      <c r="H38">
+        <v>-29329185.561714012</v>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-3455156</v>
+        <v>-1243090628.094998</v>
       </c>
       <c r="C40">
-        <v>-22986786.458053373</v>
+        <v>-1183756936.094998</v>
       </c>
       <c r="D40">
-        <v>84388273</v>
-      </c>
-      <c r="E40">
-        <v>-10167163.483834064</v>
-      </c>
-      <c r="F40">
-        <v>2223157.3413302144</v>
+        <v>-1295333262.094998</v>
+      </c>
+      <c r="G40">
+        <v>-1225723329.254002</v>
+      </c>
+      <c r="H40">
+        <v>76238.94057833671</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
+      </c>
+      <c r="B41">
+        <v>-55751723.355044454</v>
+      </c>
+      <c r="C41">
+        <v>-37904795.355044454</v>
+      </c>
+      <c r="D41">
+        <v>-73421465.35504445</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-2782559</v>
+        <v>-1187338904.7399538</v>
       </c>
       <c r="C42">
-        <v>1054546.5472940092</v>
+        <v>-1145852140.7399538</v>
       </c>
       <c r="D42">
-        <v>1662597</v>
-      </c>
-      <c r="E42">
-        <v>698203.4800319875</v>
+        <v>-1221911796.7399538</v>
+      </c>
+      <c r="G42">
+        <v>-1225723329.254002</v>
+      </c>
+      <c r="H42">
+        <v>76238.94057833671</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>48121132</v>
+        <v>-42325410.84435105</v>
       </c>
       <c r="C43">
-        <v>34357068.87073227</v>
+        <v>-350077016.84435105</v>
       </c>
       <c r="D43">
-        <v>-12097729</v>
-      </c>
-      <c r="E43">
-        <v>14953093.718299197</v>
+        <v>147931436.15564892</v>
+      </c>
+      <c r="G43">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="H43">
+        <v>-29252946.621135674</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
-      </c>
-      <c r="B44">
-        <v>-1152523</v>
-      </c>
-      <c r="C44">
-        <v>3397315.362879105</v>
-      </c>
-      <c r="D44">
-        <v>2011430</v>
-      </c>
-      <c r="E44">
-        <v>1891743.2350030025</v>
-      </c>
-      <c r="F44">
-        <v>1944739.5605358195</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v xml:space="preserve">    Türev Yükümlülüklerdeki Artış (Azalış)</v>
-      </c>
-    </row>
+        <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">    Devlet Teşvik ve Yardımlarındaki Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
+      </c>
+      <c r="B46">
+        <v>-42325410.84435105</v>
+      </c>
+      <c r="C46">
+        <v>-350077016.84435105</v>
+      </c>
+      <c r="D46">
+        <v>147931436.15564892</v>
+      </c>
+      <c r="G46">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="H46">
+        <v>-29252946.621135674</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
-      </c>
-      <c r="B47">
-        <v>5226150</v>
-      </c>
-      <c r="C47">
-        <v>-814356.3278095091</v>
-      </c>
-      <c r="D47">
-        <v>-3350758</v>
-      </c>
-      <c r="E47">
-        <v>22980938.815323275</v>
+        <v xml:space="preserve">    Azınlık Payları</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
+        <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>21627932</v>
+        <v>-42325410.84435105</v>
       </c>
       <c r="C48">
-        <v>-14801714.160119753</v>
+        <v>-350077016.84435105</v>
       </c>
       <c r="D48">
-        <v>7750984</v>
-      </c>
-      <c r="E48">
-        <v>-7205803.421674678</v>
-      </c>
-      <c r="F48">
-        <v>-545182.0921661871</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
-      </c>
-      <c r="B49">
-        <v>432324565</v>
-      </c>
-      <c r="D49">
-        <v>-171793417</v>
-      </c>
-    </row>
+        <v>147931436.15564892</v>
+      </c>
+      <c r="G48">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="H48">
+        <v>-29252946.621135674</v>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-      <c r="B54">
-        <v>-15886031</v>
-      </c>
-      <c r="C54">
-        <v>-56063472.4671203</v>
-      </c>
-      <c r="D54">
-        <v>305944</v>
-      </c>
-      <c r="E54">
-        <v>-392740.6267164124</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v xml:space="preserve">    Kira Ödemeleri</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v xml:space="preserve">    Alınan Kira</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve/veya Müşterek Faaliyetlerin Sermaye Artırımına Katılımdan Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B67">
-        <v>-20631</v>
-      </c>
-      <c r="C67">
-        <v>440001941.0163779</v>
-      </c>
-      <c r="D67">
-        <v>299098956</v>
-      </c>
-      <c r="E67">
-        <v>-419096436.68665034</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B78">
-        <v>-20631</v>
-      </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>-533602.3510203849</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B79">
-        <v>0</v>
-      </c>
-      <c r="D79">
-        <v>637035013</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B80">
-        <v>0</v>
-      </c>
-      <c r="D80">
-        <v>-337936057</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="C98">
-        <v>440001941.0163779</v>
-      </c>
-      <c r="E98">
-        <v>-419096436.68665034</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B101">
-        <v>-8413859</v>
-      </c>
-      <c r="C101">
-        <v>-393123967.5380478</v>
-      </c>
-      <c r="D101">
-        <v>-141463187</v>
-      </c>
-      <c r="E101">
-        <v>-24875367.080108255</v>
-      </c>
-      <c r="F101">
-        <v>-262545.2932635527</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
-      </c>
-      <c r="E106">
-        <v>105777032.1699209</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B110">
-        <v>-25323360</v>
-      </c>
-      <c r="C110">
-        <v>-386910430.07736766</v>
-      </c>
-      <c r="D110">
-        <v>-140165635</v>
-      </c>
-      <c r="E110">
-        <v>-77920649.28914274</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-      <c r="B118">
-        <v>-4733301</v>
-      </c>
-      <c r="C118">
-        <v>-18334163.55057529</v>
-      </c>
-      <c r="D118">
-        <v>-2152753</v>
-      </c>
-      <c r="E118">
-        <v>-57320745.365485914</v>
-      </c>
-      <c r="F118">
-        <v>-262545.2932635527</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B119">
-        <v>21642802</v>
-      </c>
-      <c r="C119">
-        <v>12120626.089895187</v>
-      </c>
-      <c r="D119">
-        <v>855201</v>
-      </c>
-      <c r="E119">
-        <v>4588995.404599487</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B125">
-        <v>408004044</v>
-      </c>
-      <c r="D125">
-        <v>-13851704</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B127">
-        <v>408004044</v>
-      </c>
-      <c r="C127">
-        <v>71792030.29700586</v>
-      </c>
-      <c r="D127">
-        <v>-13851704</v>
-      </c>
-      <c r="E127">
-        <v>20840351.6418991</v>
-      </c>
-      <c r="F127">
-        <v>269050.98837464105</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B128">
-        <v>87971617</v>
-      </c>
-      <c r="D128">
-        <v>21192104</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B129">
-        <v>487939473</v>
-      </c>
-      <c r="D129">
-        <v>9282164</v>
+        <v xml:space="preserve">    Amortisman</v>
+      </c>
+      <c r="B50">
+        <v>3537156.940245371</v>
+      </c>
+      <c r="C50">
+        <v>2562427.631838289</v>
+      </c>
+      <c r="D50">
+        <v>2535424.940245371</v>
+      </c>
+      <c r="G50">
+        <v>2040846.2897062215</v>
+      </c>
+      <c r="H50">
+        <v>141402.56202136108</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:H129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3980,6 +3370,8 @@
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3987,18 +3379,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -4012,10 +3410,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>416438534</v>
+        <v>466237159</v>
+      </c>
+      <c r="C3">
+        <v>445645040.2650864</v>
       </c>
       <c r="D3">
-        <v>-171487473</v>
+        <v>86656808.51507314</v>
+      </c>
+      <c r="E3">
+        <v>-39084042</v>
+      </c>
+      <c r="F3">
+        <v>-183514577.95220006</v>
+      </c>
+      <c r="G3">
+        <v>497831583.0523014</v>
+      </c>
+      <c r="H3">
+        <v>568879.2630689241</v>
       </c>
     </row>
     <row r="4">
@@ -4023,10 +3436,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>108347048</v>
+        <v>261135023</v>
+      </c>
+      <c r="C4">
+        <v>115945861.45710342</v>
       </c>
       <c r="D4">
-        <v>573717222</v>
+        <v>147931436.15564892</v>
+      </c>
+      <c r="E4">
+        <v>451391870</v>
+      </c>
+      <c r="F4">
+        <v>613954314.0812314</v>
+      </c>
+      <c r="G4">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="H4">
+        <v>-29252946.621135674</v>
       </c>
     </row>
     <row r="5">
@@ -4034,10 +3462,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>79849594</v>
+        <v>109504691</v>
+      </c>
+      <c r="C5">
+        <v>85449766.59936278</v>
       </c>
       <c r="D5">
-        <v>-551117869</v>
+        <v>49929827.91455575</v>
+      </c>
+      <c r="E5">
+        <v>-492043727</v>
+      </c>
+      <c r="F5">
+        <v>-589769977.725725</v>
+      </c>
+      <c r="G5">
+        <v>-116941111.69951081</v>
+      </c>
+      <c r="H5">
+        <v>33126389.05043158</v>
       </c>
     </row>
     <row r="6">
@@ -4045,10 +3488,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>592744</v>
+        <v>1655951</v>
+      </c>
+      <c r="C6">
+        <v>634315.5164091716</v>
       </c>
       <c r="D6">
-        <v>567511</v>
+        <v>2535424.940245371</v>
+      </c>
+      <c r="E6">
+        <v>654219</v>
+      </c>
+      <c r="F6">
+        <v>607312.8248162536</v>
+      </c>
+      <c r="G6">
+        <v>2040846.2897062215</v>
+      </c>
+      <c r="H6">
+        <v>141402.56202136108</v>
       </c>
     </row>
     <row r="7">
@@ -4056,10 +3514,22 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>234705</v>
+        <v>4076567</v>
+      </c>
+      <c r="C7">
+        <v>251165.80392009811</v>
       </c>
       <c r="D7">
-        <v>56503</v>
+        <v>6006875.089695977</v>
+      </c>
+      <c r="E7">
+        <v>2423525</v>
+      </c>
+      <c r="F7">
+        <v>60465.782232578356</v>
+      </c>
+      <c r="G7">
+        <v>1672803.0130881337</v>
       </c>
     </row>
     <row r="8">
@@ -4067,10 +3537,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-198514</v>
+        <v>658510</v>
+      </c>
+      <c r="C8">
+        <v>-212436.58379410047</v>
       </c>
       <c r="D8">
-        <v>887983</v>
+        <v>-178442.76277437698</v>
+      </c>
+      <c r="E8">
+        <v>1191509</v>
+      </c>
+      <c r="F8">
+        <v>950260.8127751027</v>
+      </c>
+      <c r="G8">
+        <v>7210899.469994622</v>
+      </c>
+      <c r="H8">
+        <v>1021296.3345542096</v>
       </c>
     </row>
     <row r="9">
@@ -4093,10 +3578,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-27667338</v>
+        <v>-228829062</v>
+      </c>
+      <c r="C12">
+        <v>-29607759.48999416</v>
       </c>
       <c r="D12">
-        <v>55521980</v>
+        <v>40498428.82024947</v>
+      </c>
+      <c r="E12">
+        <v>67378004</v>
+      </c>
+      <c r="F12">
+        <v>59415959.361477636</v>
+      </c>
+      <c r="G12">
+        <v>66848359.422559746</v>
+      </c>
+      <c r="H12">
+        <v>690736.0359347387</v>
       </c>
     </row>
     <row r="13">
@@ -4114,10 +3614,25 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
-        <v>5143865</v>
+        <v>11112584</v>
+      </c>
+      <c r="C15">
+        <v>5504624.903523382</v>
       </c>
       <c r="D15">
-        <v>72388067</v>
+        <v>175287522.70143178</v>
+      </c>
+      <c r="E15">
+        <v>157725487</v>
+      </c>
+      <c r="F15">
+        <v>77464932.75506242</v>
+      </c>
+      <c r="G15">
+        <v>92958258.83139104</v>
+      </c>
+      <c r="H15">
+        <v>31122195.531388473</v>
       </c>
     </row>
     <row r="16">
@@ -4135,10 +3650,22 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B18">
+        <v>-3743276</v>
+      </c>
+      <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>-641911422</v>
+        <v>-79990137.62707785</v>
+      </c>
+      <c r="E18">
+        <v>-686931248</v>
+      </c>
+      <c r="F18">
+        <v>-686931247.106467</v>
+      </c>
+      <c r="G18">
+        <v>-633330623.1428425</v>
       </c>
     </row>
     <row r="19">
@@ -4151,16 +3678,40 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>514675402</v>
+        <v>887309029</v>
+      </c>
+      <c r="C20">
+        <v>550771654.209453</v>
       </c>
       <c r="D20">
-        <v>618939283</v>
+        <v>1295333262.094998</v>
+      </c>
+      <c r="E20">
+        <v>939551663</v>
+      </c>
+      <c r="F20">
+        <v>662347979.772157</v>
+      </c>
+      <c r="G20">
+        <v>1225723329.254002</v>
+      </c>
+      <c r="H20">
+        <v>-76238.94057833671</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
+      <c r="D21">
+        <v>-803577988.905617</v>
+      </c>
+      <c r="G21">
+        <v>-910353678.111134</v>
+      </c>
+      <c r="H21">
+        <v>226997.5271111339</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -4169,8 +3720,20 @@
       <c r="B22">
         <v>0</v>
       </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
       <c r="D22">
-        <v>-345414094</v>
+        <v>-585985116.4365956</v>
+      </c>
+      <c r="E22">
+        <v>-457691363</v>
+      </c>
+      <c r="F22">
+        <v>-369639371.14608693</v>
+      </c>
+      <c r="G22">
+        <v>30288693.27372385</v>
       </c>
     </row>
     <row r="23">
@@ -4203,10 +3766,22 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>244127923</v>
+        <v>160034284</v>
+      </c>
+      <c r="C28">
+        <v>261249594.34029445</v>
       </c>
       <c r="D28">
-        <v>-194392770</v>
+        <v>-111204455.55513154</v>
+      </c>
+      <c r="E28">
+        <v>53641313</v>
+      </c>
+      <c r="F28">
+        <v>-208026315.38869956</v>
+      </c>
+      <c r="G28">
+        <v>66600938.79499527</v>
       </c>
     </row>
     <row r="29">
@@ -4224,10 +3799,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>155632921</v>
+        <v>144479957</v>
+      </c>
+      <c r="C31">
+        <v>166548082.5691746</v>
       </c>
       <c r="D31">
-        <v>-275495861</v>
+        <v>-162813716.3654689</v>
+      </c>
+      <c r="E31">
+        <v>-343381937</v>
+      </c>
+      <c r="F31">
+        <v>-294817491.7650864</v>
+      </c>
+      <c r="G31">
+        <v>-31679781.619496454</v>
+      </c>
+      <c r="H31">
+        <v>-7181353.509643215</v>
       </c>
     </row>
     <row r="32">
@@ -4240,10 +3830,22 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-525081</v>
+        <v>-3066479</v>
+      </c>
+      <c r="C33">
+        <v>-561907.0385725443</v>
       </c>
       <c r="D33">
-        <v>-333014</v>
+        <v>-1075155.005045719</v>
+      </c>
+      <c r="E33">
+        <v>-449888</v>
+      </c>
+      <c r="F33">
+        <v>-356369.608771213</v>
+      </c>
+      <c r="G33">
+        <v>-52984.89199088186</v>
       </c>
     </row>
     <row r="34">
@@ -4266,10 +3868,22 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>40173899</v>
+        <v>28799305</v>
+      </c>
+      <c r="C37">
+        <v>42991455.82301112</v>
       </c>
       <c r="D37">
-        <v>3361629</v>
+        <v>52958153.4266834</v>
+      </c>
+      <c r="E37">
+        <v>8337895</v>
+      </c>
+      <c r="F37">
+        <v>3597393.53770101</v>
+      </c>
+      <c r="G37">
+        <v>77397493.148631</v>
       </c>
     </row>
     <row r="38">
@@ -4282,10 +3896,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-18738792</v>
+        <v>-11935971</v>
+      </c>
+      <c r="C39">
+        <v>-20053018.713583022</v>
       </c>
       <c r="D39">
-        <v>-2290321</v>
+        <v>-494264.23159081023</v>
+      </c>
+      <c r="E39">
+        <v>-3253616</v>
+      </c>
+      <c r="F39">
+        <v>-2450950.4066810803</v>
+      </c>
+      <c r="G39">
+        <v>-3838473.625284943</v>
       </c>
     </row>
     <row r="40">
@@ -4293,10 +3919,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-3455156</v>
+        <v>8884370</v>
+      </c>
+      <c r="C40">
+        <v>-3697479.9616938303</v>
       </c>
       <c r="D40">
-        <v>84388273</v>
+        <v>-24598942.077401843</v>
+      </c>
+      <c r="E40">
+        <v>235384492</v>
+      </c>
+      <c r="F40">
+        <v>90306761.3790661</v>
+      </c>
+      <c r="G40">
+        <v>-10880227.477063753</v>
+      </c>
+      <c r="H40">
+        <v>2379076.290986861</v>
       </c>
     </row>
     <row r="41">
@@ -4309,10 +3950,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-2782559</v>
+        <v>2997595</v>
+      </c>
+      <c r="C42">
+        <v>-2977711.033808842</v>
       </c>
       <c r="D42">
-        <v>1662597</v>
+        <v>1128506.1303434677</v>
+      </c>
+      <c r="E42">
+        <v>3214182</v>
+      </c>
+      <c r="F42">
+        <v>1779201.6024377127</v>
+      </c>
+      <c r="G42">
+        <v>747171.2931639475</v>
       </c>
     </row>
     <row r="43">
@@ -4320,10 +3973,22 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B43">
-        <v>48121132</v>
+        <v>-47445218</v>
+      </c>
+      <c r="C43">
+        <v>51496060.17905523</v>
       </c>
       <c r="D43">
-        <v>-12097729</v>
+        <v>36766668.04395155</v>
+      </c>
+      <c r="E43">
+        <v>142636557</v>
+      </c>
+      <c r="F43">
+        <v>-12946191.303519245</v>
+      </c>
+      <c r="G43">
+        <v>16001814.212944703</v>
       </c>
     </row>
     <row r="44">
@@ -4331,10 +3996,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-1152523</v>
+        <v>13545917</v>
+      </c>
+      <c r="C44">
+        <v>-1233354.065023767</v>
       </c>
       <c r="D44">
-        <v>2011430</v>
+        <v>3635582.7284788573</v>
+      </c>
+      <c r="E44">
+        <v>5900417</v>
+      </c>
+      <c r="F44">
+        <v>2152499.6611874606</v>
+      </c>
+      <c r="G44">
+        <v>2024418.7828548015</v>
+      </c>
+      <c r="H44">
+        <v>2081131.9534615683</v>
       </c>
     </row>
     <row r="45">
@@ -4352,10 +4032,22 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>5226150</v>
+        <v>-11840718</v>
+      </c>
+      <c r="C47">
+        <v>5592680.880922949</v>
       </c>
       <c r="D47">
-        <v>-3350758</v>
+        <v>-871470.4064749123</v>
+      </c>
+      <c r="E47">
+        <v>-3041380</v>
+      </c>
+      <c r="F47">
+        <v>-3585760.110827209</v>
+      </c>
+      <c r="G47">
+        <v>24592684.316010553</v>
       </c>
     </row>
     <row r="48">
@@ -4363,10 +4055,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>21627932</v>
+        <v>35615526</v>
+      </c>
+      <c r="C48">
+        <v>23144785.700812574</v>
       </c>
       <c r="D48">
-        <v>7750984</v>
+        <v>-15839817.798606666</v>
+      </c>
+      <c r="E48">
+        <v>8294591</v>
+      </c>
+      <c r="F48">
+        <v>8294591.625793305</v>
+      </c>
+      <c r="G48">
+        <v>-7711175.344773713</v>
+      </c>
+      <c r="H48">
+        <v>-583417.9010321953</v>
       </c>
     </row>
     <row r="49">
@@ -4374,10 +4081,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>432324565</v>
-      </c>
-      <c r="D49">
-        <v>-171793417</v>
+        <v>530673998</v>
+      </c>
+      <c r="C49">
+        <v>462645222.39676064</v>
+      </c>
+      <c r="E49">
+        <v>12989456</v>
+      </c>
+      <c r="F49">
+        <v>-183841979.03319335</v>
       </c>
     </row>
     <row r="50">
@@ -4405,10 +4118,22 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-15886031</v>
+        <v>-64436839</v>
+      </c>
+      <c r="C54">
+        <v>-17000182.13167423</v>
       </c>
       <c r="D54">
-        <v>305944</v>
+        <v>-59995428.869246736</v>
+      </c>
+      <c r="E54">
+        <v>-52073498</v>
+      </c>
+      <c r="F54">
+        <v>327401.0809932916</v>
+      </c>
+      <c r="G54">
+        <v>-420285.10360371904</v>
       </c>
     </row>
     <row r="55">
@@ -4472,10 +4197,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-20631</v>
+        <v>-96454822</v>
+      </c>
+      <c r="C67">
+        <v>-22077.934857269953</v>
       </c>
       <c r="D67">
-        <v>299098956</v>
+        <v>470861043.6155265</v>
+      </c>
+      <c r="E67">
+        <v>408127961</v>
+      </c>
+      <c r="F67">
+        <v>320075966.5767753</v>
+      </c>
+      <c r="G67">
+        <v>-448489352.3378327</v>
       </c>
     </row>
     <row r="68">
@@ -4522,6 +4259,9 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="B76">
+        <v>-84999994</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4533,10 +4273,19 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-20631</v>
-      </c>
-      <c r="D78">
+        <v>-11454828</v>
+      </c>
+      <c r="C78">
+        <v>-22077.934857269953</v>
+      </c>
+      <c r="E78">
         <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>-571026.0261506545</v>
       </c>
     </row>
     <row r="79">
@@ -4546,8 +4295,14 @@
       <c r="B79">
         <v>0</v>
       </c>
-      <c r="D79">
-        <v>637035013</v>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>769764830</v>
+      </c>
+      <c r="F79">
+        <v>681712835.9659792</v>
       </c>
     </row>
     <row r="80">
@@ -4557,8 +4312,14 @@
       <c r="B80">
         <v>0</v>
       </c>
-      <c r="D80">
-        <v>-337936057</v>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>-361636869</v>
+      </c>
+      <c r="F80">
+        <v>-361636869.38920385</v>
       </c>
     </row>
     <row r="81">
@@ -4649,6 +4410,12 @@
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="D98">
+        <v>470861043.6155265</v>
+      </c>
+      <c r="G98">
+        <v>-448489352.3378327</v>
       </c>
     </row>
     <row r="99">
@@ -4662,10 +4429,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-8413859</v>
+        <v>1664731830</v>
+      </c>
+      <c r="C101">
+        <v>-9003956.710787382</v>
       </c>
       <c r="D101">
-        <v>-141463187</v>
+        <v>-420695329.656174</v>
+      </c>
+      <c r="E101">
+        <v>-394004873</v>
+      </c>
+      <c r="F101">
+        <v>-151384568.23652744</v>
+      </c>
+      <c r="G101">
+        <v>-26619976.440565534</v>
+      </c>
+      <c r="H101">
+        <v>-280958.6487206414</v>
       </c>
     </row>
     <row r="102">
@@ -4682,16 +4464,28 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B104">
+        <v>2070724296</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
         <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
+      <c r="B105">
+        <v>105652000</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
+      <c r="G106">
+        <v>113195600.09901904</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -4713,10 +4507,22 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-25323360</v>
+        <v>-376688591</v>
+      </c>
+      <c r="C110">
+        <v>-27099388.902486335</v>
       </c>
       <c r="D110">
-        <v>-140165635</v>
+        <v>-414046011.8678893</v>
+      </c>
+      <c r="E110">
+        <v>-380085109</v>
+      </c>
+      <c r="F110">
+        <v>-149996013.7054858</v>
+      </c>
+      <c r="G110">
+        <v>-83385537.25179932</v>
       </c>
     </row>
     <row r="111">
@@ -4753,16 +4559,34 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
+      <c r="B117">
+        <v>-353279717</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-4733301</v>
+        <v>-11480362</v>
+      </c>
+      <c r="C118">
+        <v>-5065266.401912206</v>
       </c>
       <c r="D118">
-        <v>-2152753</v>
+        <v>-19620012.04653843</v>
+      </c>
+      <c r="E118">
+        <v>-17335897</v>
+      </c>
+      <c r="F118">
+        <v>-2303734.2105468693</v>
+      </c>
+      <c r="G118">
+        <v>-61340879.36354789</v>
+      </c>
+      <c r="H118">
+        <v>-280958.6487206414</v>
       </c>
     </row>
     <row r="119">
@@ -4770,16 +4594,31 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>21642802</v>
+        <v>229804204</v>
+      </c>
+      <c r="C119">
+        <v>23160698.59361116</v>
       </c>
       <c r="D119">
-        <v>855201</v>
+        <v>12970694.258253722</v>
+      </c>
+      <c r="E119">
+        <v>3416133</v>
+      </c>
+      <c r="F119">
+        <v>915179.6795052164</v>
+      </c>
+      <c r="G119">
+        <v>4910840.075762621</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
         <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -4806,10 +4645,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>408004044</v>
-      </c>
-      <c r="D125">
-        <v>-13851704</v>
+        <v>2034514167</v>
+      </c>
+      <c r="C125">
+        <v>436619005.61944175</v>
+      </c>
+      <c r="E125">
+        <v>-24960954</v>
+      </c>
+      <c r="F125">
+        <v>-14823179.61195219</v>
       </c>
     </row>
     <row r="126">
@@ -4822,10 +4667,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>408004044</v>
+        <v>2034514167</v>
+      </c>
+      <c r="C127">
+        <v>436619005.61944175</v>
       </c>
       <c r="D127">
-        <v>-13851704</v>
+        <v>76827093.60517891</v>
+      </c>
+      <c r="E127">
+        <v>-24960954</v>
+      </c>
+      <c r="F127">
+        <v>-14823179.61195219</v>
+      </c>
+      <c r="G127">
+        <v>22301969.170299415</v>
+      </c>
+      <c r="H127">
+        <v>287920.6143482827</v>
       </c>
     </row>
     <row r="128">
@@ -4833,10 +4693,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>87971617</v>
-      </c>
-      <c r="D128">
-        <v>21192104</v>
+        <v>94141419</v>
+      </c>
+      <c r="C128">
+        <v>94141419.67983626</v>
+      </c>
+      <c r="E128">
+        <v>22678391</v>
+      </c>
+      <c r="F128">
+        <v>22678391.333454024</v>
       </c>
     </row>
     <row r="129">
@@ -4844,22 +4710,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>487939473</v>
-      </c>
-      <c r="D129">
-        <v>9282164</v>
+        <v>2114443373</v>
+      </c>
+      <c r="C129">
+        <v>522160627.1719563</v>
+      </c>
+      <c r="E129">
+        <v>965480</v>
+      </c>
+      <c r="F129">
+        <v>9933159.426421225</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:H129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4867,6 +4739,8 @@
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4874,18 +4748,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="F1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -4899,16 +4779,16 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>668903536.2857959</v>
+        <v>20592118.734913588</v>
       </c>
       <c r="C3">
-        <v>80977529.285796</v>
+        <v>445645040.2650864</v>
       </c>
       <c r="E3">
-        <v>465204896.0353741</v>
+        <v>144430535.95220006</v>
       </c>
       <c r="F3">
-        <v>531596.2816381938</v>
+        <v>-183514577.95220006</v>
       </c>
     </row>
     <row r="4">
@@ -4916,16 +4796,16 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-327133809.0927894</v>
+        <v>145189161.54289657</v>
       </c>
       <c r="C4">
-        <v>138236364.90721056</v>
+        <v>115945861.45710342</v>
       </c>
       <c r="E4">
-        <v>512245894.838352</v>
+        <v>-162562444.08123136</v>
       </c>
       <c r="F4">
-        <v>-27335778.71491546</v>
+        <v>613954314.0812314</v>
       </c>
     </row>
     <row r="5">
@@ -4933,16 +4813,16 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>677625009.8387163</v>
+        <v>24054924.400637224</v>
       </c>
       <c r="C5">
-        <v>46657546.83871628</v>
+        <v>85449766.59936278</v>
       </c>
       <c r="E5">
-        <v>-109277071.93040152</v>
+        <v>97726250.72572505</v>
       </c>
       <c r="F5">
-        <v>30955365.02475049</v>
+        <v>-589769977.725725</v>
       </c>
     </row>
     <row r="6">
@@ -4950,16 +4830,16 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>2394492.275397212</v>
+        <v>1021635.4835908284</v>
       </c>
       <c r="C6">
-        <v>2369259.275397212</v>
+        <v>634315.5164091716</v>
       </c>
       <c r="E6">
-        <v>1907094.122486034</v>
+        <v>46906.17518374638</v>
       </c>
       <c r="F6">
-        <v>132135.37751254314</v>
+        <v>607312.8248162536</v>
       </c>
     </row>
     <row r="7">
@@ -4967,13 +4847,16 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>5791400.914513058</v>
+        <v>3825401.196079902</v>
       </c>
       <c r="C7">
-        <v>5613198.914513058</v>
+        <v>251165.80392009811</v>
       </c>
       <c r="E7">
-        <v>1563171.5188097453</v>
+        <v>2363059.2177674216</v>
+      </c>
+      <c r="F7">
+        <v>60465.782232578356</v>
       </c>
     </row>
     <row r="8">
@@ -4981,16 +4864,16 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-1253245.0524151435</v>
+        <v>870946.5837941004</v>
       </c>
       <c r="C8">
-        <v>-166748.0524151434</v>
+        <v>-212436.58379410047</v>
       </c>
       <c r="E8">
-        <v>6738314.426925299</v>
+        <v>241248.18722489732</v>
       </c>
       <c r="F8">
-        <v>954363.0241870075</v>
+        <v>950260.8127751027</v>
       </c>
     </row>
     <row r="9">
@@ -5013,16 +4896,16 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-45345058.996969156</v>
+        <v>-199221302.51000583</v>
       </c>
       <c r="C12">
-        <v>37844259.003030844</v>
+        <v>-29607759.48999416</v>
       </c>
       <c r="E12">
-        <v>62467278.40093686</v>
+        <v>7962044.638522364</v>
       </c>
       <c r="F12">
-        <v>645466.8541010339</v>
+        <v>59415959.361477636</v>
       </c>
     </row>
     <row r="13">
@@ -5040,16 +4923,16 @@
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
       <c r="B15">
-        <v>96555397.20311224</v>
+        <v>5607959.096476618</v>
       </c>
       <c r="C15">
-        <v>163799599.20311224</v>
+        <v>5504624.903523382</v>
       </c>
       <c r="E15">
-        <v>86865997.67364188</v>
+        <v>80260554.24493758</v>
       </c>
       <c r="F15">
-        <v>29082521.538315304</v>
+        <v>77464932.75506242</v>
       </c>
     </row>
     <row r="16">
@@ -5067,13 +4950,16 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B18">
-        <v>567163645.994092</v>
+        <v>-3743276</v>
       </c>
       <c r="C18">
-        <v>-74747776.00590801</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>-591823654.2743243</v>
+        <v>-0.8935329914093018</v>
+      </c>
+      <c r="F18">
+        <v>-686931247.106467</v>
       </c>
     </row>
     <row r="19">
@@ -5086,44 +4972,38 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>1106176348.2627501</v>
+        <v>336537374.790547</v>
       </c>
       <c r="C20">
-        <v>1210440229.2627501</v>
+        <v>550771654.209453</v>
       </c>
       <c r="E20">
-        <v>1145392364.3366659</v>
+        <v>277203683.22784305</v>
       </c>
       <c r="F20">
-        <v>-71242.42340780962</v>
+        <v>662347979.772157</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>-750913416.3267394</v>
-      </c>
-      <c r="E21">
-        <v>-850691283.1535202</v>
-      </c>
-      <c r="F21">
-        <v>212120.6540424091</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
-        <v>-202166964.43502462</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>-547581058.4350246</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>28303645.01797733</v>
+        <v>-88051991.85391307</v>
+      </c>
+      <c r="F22">
+        <v>-369639371.14608693</v>
       </c>
     </row>
     <row r="23">
@@ -5156,13 +5036,16 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>334604310.5398691</v>
+        <v>-101215310.34029445</v>
       </c>
       <c r="C28">
-        <v>-103916382.46013086</v>
+        <v>261249594.34029445</v>
       </c>
       <c r="E28">
-        <v>62236073.12742361</v>
+        <v>261667628.38869956</v>
+      </c>
+      <c r="F28">
+        <v>-208026315.38869956</v>
       </c>
     </row>
     <row r="29">
@@ -5180,16 +5063,16 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>278985485.80624783</v>
+        <v>-22068125.569174588</v>
       </c>
       <c r="C31">
-        <v>-152143296.1937522</v>
+        <v>166548082.5691746</v>
       </c>
       <c r="E31">
-        <v>-29603564.77257269</v>
+        <v>-48564445.23491359</v>
       </c>
       <c r="F31">
-        <v>-6710704.837896678</v>
+        <v>-294817491.7650864</v>
       </c>
     </row>
     <row r="32">
@@ -5202,13 +5085,16 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1196758.9266905151</v>
+        <v>-2504571.961427456</v>
       </c>
       <c r="C33">
-        <v>-1004691.926690515</v>
+        <v>-561907.0385725443</v>
       </c>
       <c r="E33">
-        <v>-49512.3893484961</v>
+        <v>-93518.39122878702</v>
+      </c>
+      <c r="F33">
+        <v>-356369.608771213</v>
       </c>
     </row>
     <row r="34">
@@ -5231,13 +5117,16 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>86299673.16561511</v>
+        <v>-14192150.823011123</v>
       </c>
       <c r="C37">
-        <v>49487403.16561512</v>
+        <v>42991455.82301112</v>
       </c>
       <c r="E37">
-        <v>72325047.22350001</v>
+        <v>4740501.46229899</v>
+      </c>
+      <c r="F37">
+        <v>3597393.53770101</v>
       </c>
     </row>
     <row r="38">
@@ -5250,13 +5139,16 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-16910342.340226017</v>
+        <v>8117047.713583022</v>
       </c>
       <c r="C39">
-        <v>-461871.3402260186</v>
+        <v>-20053018.713583022</v>
       </c>
       <c r="E39">
-        <v>-3586909.277303941</v>
+        <v>-802665.5933189197</v>
+      </c>
+      <c r="F39">
+        <v>-2450950.4066810803</v>
       </c>
     </row>
     <row r="40">
@@ -5264,16 +5156,16 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-110830215.45805338</v>
+        <v>12581849.96169383</v>
       </c>
       <c r="C40">
-        <v>-22986786.458053373</v>
+        <v>-3697479.9616938303</v>
       </c>
       <c r="E40">
-        <v>-10167163.483834064</v>
+        <v>145077730.6209339</v>
       </c>
       <c r="F40">
-        <v>2223157.3413302144</v>
+        <v>90306761.3790661</v>
       </c>
     </row>
     <row r="41">
@@ -5286,13 +5178,16 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-3390609.4527059905</v>
+        <v>5975306.033808842</v>
       </c>
       <c r="C42">
-        <v>1054546.5472940092</v>
+        <v>-2977711.033808842</v>
       </c>
       <c r="E42">
-        <v>698203.4800319875</v>
+        <v>1434980.3975622873</v>
+      </c>
+      <c r="F42">
+        <v>1779201.6024377127</v>
       </c>
     </row>
     <row r="43">
@@ -5300,13 +5195,16 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B43">
-        <v>94575929.87073228</v>
+        <v>-98941278.17905523</v>
       </c>
       <c r="C43">
-        <v>34357068.87073227</v>
+        <v>51496060.17905523</v>
       </c>
       <c r="E43">
-        <v>14953093.718299197</v>
+        <v>155582748.30351925</v>
+      </c>
+      <c r="F43">
+        <v>-12946191.303519245</v>
       </c>
     </row>
     <row r="44">
@@ -5314,16 +5212,16 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>233362.3628791049</v>
+        <v>14779271.065023767</v>
       </c>
       <c r="C44">
-        <v>3397315.362879105</v>
+        <v>-1233354.065023767</v>
       </c>
       <c r="E44">
-        <v>1891743.2350030025</v>
+        <v>3747917.3388125394</v>
       </c>
       <c r="F44">
-        <v>1944739.5605358195</v>
+        <v>2152499.6611874606</v>
       </c>
     </row>
     <row r="45">
@@ -5341,13 +5239,16 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>7762551.672190491</v>
+        <v>-17433398.88092295</v>
       </c>
       <c r="C47">
-        <v>-814356.3278095091</v>
+        <v>5592680.880922949</v>
       </c>
       <c r="E47">
-        <v>22980938.815323275</v>
+        <v>544380.110827209</v>
+      </c>
+      <c r="F47">
+        <v>-3585760.110827209</v>
       </c>
     </row>
     <row r="48">
@@ -5355,22 +5256,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-924766.1601197533</v>
+        <v>12470740.299187426</v>
       </c>
       <c r="C48">
-        <v>-14801714.160119753</v>
+        <v>23144785.700812574</v>
       </c>
       <c r="E48">
-        <v>-7205803.421674678</v>
+        <v>-0.6257933052256703</v>
       </c>
       <c r="F48">
-        <v>-545182.0921661871</v>
+        <v>8294591.625793305</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>68028775.60323936</v>
+      </c>
+      <c r="C49">
+        <v>462645222.39676064</v>
+      </c>
+      <c r="E49">
+        <v>196831435.03319335</v>
+      </c>
+      <c r="F49">
+        <v>-183841979.03319335</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -5397,13 +5310,16 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-72255447.46712029</v>
+        <v>-47436656.86832577</v>
       </c>
       <c r="C54">
-        <v>-56063472.4671203</v>
+        <v>-17000182.13167423</v>
       </c>
       <c r="E54">
-        <v>-392740.6267164124</v>
+        <v>-52400899.080993295</v>
+      </c>
+      <c r="F54">
+        <v>327401.0809932916</v>
       </c>
     </row>
     <row r="55">
@@ -5467,13 +5383,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>140882354.01637793</v>
+        <v>-96432744.06514274</v>
       </c>
       <c r="C67">
-        <v>440001941.0163779</v>
+        <v>-22077.934857269953</v>
       </c>
       <c r="E67">
-        <v>-419096436.68665034</v>
+        <v>88051994.42322469</v>
+      </c>
+      <c r="F67">
+        <v>320075966.5767753</v>
       </c>
     </row>
     <row r="68">
@@ -5530,19 +5449,52 @@
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
+      <c r="B78">
+        <v>-11432750.06514273</v>
+      </c>
+      <c r="C78">
+        <v>-22077.934857269953</v>
+      </c>
       <c r="E78">
-        <v>-533602.3510203849</v>
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>88051994.03402078</v>
+      </c>
+      <c r="F79">
+        <v>681712835.9659792</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
         <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0.38920384645462036</v>
+      </c>
+      <c r="F80">
+        <v>-361636869.38920385</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -5632,12 +5584,6 @@
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="C98">
-        <v>440001941.0163779</v>
-      </c>
-      <c r="E98">
-        <v>-419096436.68665034</v>
       </c>
     </row>
     <row r="99">
@@ -5651,16 +5597,16 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-260074639.5380478</v>
+        <v>1673735786.7107873</v>
       </c>
       <c r="C101">
-        <v>-393123967.5380478</v>
+        <v>-9003956.710787382</v>
       </c>
       <c r="E101">
-        <v>-24875367.080108255</v>
+        <v>-242620304.76347256</v>
       </c>
       <c r="F101">
-        <v>-262545.2932635527</v>
+        <v>-151384568.23652744</v>
       </c>
     </row>
     <row r="102">
@@ -5687,9 +5633,6 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="E106">
-        <v>105777032.1699209</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5711,13 +5654,16 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-272068155.07736766</v>
+        <v>-349589202.0975137</v>
       </c>
       <c r="C110">
-        <v>-386910430.07736766</v>
+        <v>-27099388.902486335</v>
       </c>
       <c r="E110">
-        <v>-77920649.28914274</v>
+        <v>-230089095.2945142</v>
+      </c>
+      <c r="F110">
+        <v>-149996013.7054858</v>
       </c>
     </row>
     <row r="111">
@@ -5760,16 +5706,16 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-20914711.55057529</v>
+        <v>-6415095.598087794</v>
       </c>
       <c r="C118">
-        <v>-18334163.55057529</v>
+        <v>-5065266.401912206</v>
       </c>
       <c r="E118">
-        <v>-57320745.365485914</v>
+        <v>-15032162.78945313</v>
       </c>
       <c r="F118">
-        <v>-262545.2932635527</v>
+        <v>-2303734.2105468693</v>
       </c>
     </row>
     <row r="119">
@@ -5777,13 +5723,16 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>32908227.08989519</v>
+        <v>206643505.40638885</v>
       </c>
       <c r="C119">
-        <v>12120626.089895187</v>
+        <v>23160698.59361116</v>
       </c>
       <c r="E119">
-        <v>4588995.404599487</v>
+        <v>2500953.3204947836</v>
+      </c>
+      <c r="F119">
+        <v>915179.6795052164</v>
       </c>
     </row>
     <row r="120">
@@ -5815,6 +5764,18 @@
       <c r="A125" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
+      <c r="B125">
+        <v>1597895161.3805583</v>
+      </c>
+      <c r="C125">
+        <v>436619005.61944175</v>
+      </c>
+      <c r="E125">
+        <v>-10137774.38804781</v>
+      </c>
+      <c r="F125">
+        <v>-14823179.61195219</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -5826,31 +5787,1148 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>493647778.2970059</v>
+        <v>1597895161.3805583</v>
       </c>
       <c r="C127">
-        <v>71792030.29700586</v>
+        <v>436619005.61944175</v>
       </c>
       <c r="E127">
-        <v>20840351.6418991</v>
+        <v>-10137774.38804781</v>
       </c>
       <c r="F127">
-        <v>269050.98837464105</v>
+        <v>-14823179.61195219</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B128">
+        <v>-0.6798362582921982</v>
+      </c>
+      <c r="C128">
+        <v>94141419.67983626</v>
+      </c>
+      <c r="E128">
+        <v>-0.33345402404665947</v>
+      </c>
+      <c r="F128">
+        <v>22678391.333454024</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B129">
+        <v>1592282745.8280437</v>
+      </c>
+      <c r="C129">
+        <v>522160627.1719563</v>
+      </c>
+      <c r="E129">
+        <v>-8967679.426421225</v>
+      </c>
+      <c r="F129">
+        <v>9933159.426421225</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H129"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H129"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
+    <col min="2" max="2" customWidth="1" width="20"/>
+    <col min="3" max="3" customWidth="1" width="20"/>
+    <col min="4" max="4" customWidth="1" width="20"/>
+    <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Kalem</v>
+      </c>
+      <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="F1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2024/12</v>
+      </c>
+      <c r="H1" t="str">
+        <v>2023/12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B3">
+        <v>591978009.5150732</v>
+      </c>
+      <c r="C3">
+        <v>715816426.7323596</v>
+      </c>
+      <c r="D3">
+        <v>86656808.51507314</v>
+      </c>
+      <c r="G3">
+        <v>497831583.0523014</v>
+      </c>
+      <c r="H3">
+        <v>568879.2630689241</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">    Dönem Karı (Zararı)</v>
+      </c>
+      <c r="B4">
+        <v>-42325410.84435105</v>
+      </c>
+      <c r="C4">
+        <v>-350077016.468479</v>
+      </c>
+      <c r="D4">
+        <v>147931436.15564892</v>
+      </c>
+      <c r="G4">
+        <v>548171755.9568169</v>
+      </c>
+      <c r="H4">
+        <v>-29252946.621135674</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B5">
+        <v>651478245.9145558</v>
+      </c>
+      <c r="C5">
+        <v>725149572.2396436</v>
+      </c>
+      <c r="D5">
+        <v>49929827.91455575</v>
+      </c>
+      <c r="G5">
+        <v>-116941111.69951081</v>
+      </c>
+      <c r="H5">
+        <v>33126389.05043158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B6">
+        <v>3537156.940245371</v>
+      </c>
+      <c r="C6">
+        <v>2562427.631838289</v>
+      </c>
+      <c r="D6">
+        <v>2535424.940245371</v>
+      </c>
+      <c r="G6">
+        <v>2040846.2897062215</v>
+      </c>
+      <c r="H6">
+        <v>141402.56202136108</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B7">
+        <v>7659917.089695977</v>
+      </c>
+      <c r="C7">
+        <v>6197575.111383498</v>
+      </c>
+      <c r="D7">
+        <v>6006875.089695977</v>
+      </c>
+      <c r="G7">
+        <v>1672803.0130881337</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B8">
+        <v>-711441.7627743769</v>
+      </c>
+      <c r="C8">
+        <v>-1341140.15934358</v>
+      </c>
+      <c r="D8">
+        <v>-178442.76277437698</v>
+      </c>
+      <c r="G8">
+        <v>7210899.469994622</v>
+      </c>
+      <c r="H8">
+        <v>1021296.3345542096</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">    Kar Payı (Geliri) Gideri ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan (Gelirler) Giderler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve">    Pazarlıklı Satın Alım Sonucu Oluşan Kazanç ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B12">
+        <v>-255708637.17975053</v>
+      </c>
+      <c r="C12">
+        <v>-48525290.03122233</v>
+      </c>
+      <c r="D12">
+        <v>40498428.82024947</v>
+      </c>
+      <c r="G12">
+        <v>66848359.422559746</v>
+      </c>
+      <c r="H12">
+        <v>690736.0359347387</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Gelirler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">    Takas İşlemlerinden Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B15">
+        <v>28674619.70143178</v>
+      </c>
+      <c r="C15">
+        <v>103327214.84989275</v>
+      </c>
+      <c r="D15">
+        <v>175287522.70143178</v>
+      </c>
+      <c r="G15">
+        <v>92958258.83139104</v>
+      </c>
+      <c r="H15">
+        <v>31122195.531388473</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v xml:space="preserve">    Pay Bazlı Ödemeler İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v xml:space="preserve">    Hibe Krediler ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B18">
+        <v>603197834.3729222</v>
+      </c>
+      <c r="C18">
+        <v>606941109.4793892</v>
+      </c>
+      <c r="D18">
+        <v>-79990137.62707785</v>
+      </c>
+      <c r="G18">
+        <v>-633330623.1428425</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B20">
+        <v>1243090628.094998</v>
+      </c>
+      <c r="C20">
+        <v>1183756936.5322938</v>
+      </c>
+      <c r="D20">
+        <v>1295333262.094998</v>
+      </c>
+      <c r="G20">
+        <v>1225723329.254002</v>
+      </c>
+      <c r="H20">
+        <v>-76238.94057833671</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
+      </c>
+      <c r="D21">
+        <v>-803577988.905617</v>
+      </c>
+      <c r="G21">
+        <v>-910353678.111134</v>
+      </c>
+      <c r="H21">
+        <v>226997.5271111339</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B22">
+        <v>-128293753.43659556</v>
+      </c>
+      <c r="C22">
+        <v>-216345745.29050863</v>
+      </c>
+      <c r="D22">
+        <v>-585985116.4365956</v>
+      </c>
+      <c r="G22">
+        <v>30288693.27372385</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">    İştirak, İş ortaklığı ve Finansal Yatırımların Elden Çıkarılmasından veya Paylarındaki Değişim Sebebi ile Oluşan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların veya Müşterek Faaliyetlerin Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
+      </c>
+      <c r="B28">
+        <v>-4811484.555131555</v>
+      </c>
+      <c r="C28">
+        <v>358071454.17386246</v>
+      </c>
+      <c r="D28">
+        <v>-111204455.55513154</v>
+      </c>
+      <c r="G28">
+        <v>66600938.79499527</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabındaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B31">
+        <v>325048177.63453114</v>
+      </c>
+      <c r="C31">
+        <v>298551857.9687921</v>
+      </c>
+      <c r="D31">
+        <v>-162813716.3654689</v>
+      </c>
+      <c r="G31">
+        <v>-31679781.619496454</v>
+      </c>
+      <c r="H31">
+        <v>-7181353.509643215</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B33">
+        <v>-3691746.005045719</v>
+      </c>
+      <c r="C33">
+        <v>-1280692.4348470503</v>
+      </c>
+      <c r="D33">
+        <v>-1075155.005045719</v>
+      </c>
+      <c r="G33">
+        <v>-52984.89199088186</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B37">
+        <v>73419563.4266834</v>
+      </c>
+      <c r="C37">
+        <v>92352215.71199352</v>
+      </c>
+      <c r="D37">
+        <v>52958153.4266834</v>
+      </c>
+      <c r="G37">
+        <v>77397493.148631</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">    Canlı Varlıklardaki Azalış (Artış)</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
+      </c>
+      <c r="B39">
+        <v>-9176619.231590811</v>
+      </c>
+      <c r="C39">
+        <v>-18096332.538492754</v>
+      </c>
+      <c r="D39">
+        <v>-494264.23159081023</v>
+      </c>
+      <c r="G39">
+        <v>-3838473.625284943</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B40">
+        <v>-251099064.07740185</v>
+      </c>
+      <c r="C40">
+        <v>-118603183.41816176</v>
+      </c>
+      <c r="D40">
+        <v>-24598942.077401843</v>
+      </c>
+      <c r="G40">
+        <v>-10880227.477063753</v>
+      </c>
+      <c r="H40">
+        <v>2379076.290986861</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlardaki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
+      </c>
+      <c r="B42">
+        <v>911919.1303434677</v>
+      </c>
+      <c r="C42">
+        <v>-3628406.5059030866</v>
+      </c>
+      <c r="D42">
+        <v>1128506.1303434677</v>
+      </c>
+      <c r="G42">
+        <v>747171.2931639475</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
+      </c>
+      <c r="B43">
+        <v>-153315106.95604846</v>
+      </c>
+      <c r="C43">
+        <v>101208919.52652602</v>
+      </c>
+      <c r="D43">
+        <v>36766668.04395155</v>
+      </c>
+      <c r="G43">
+        <v>16001814.212944703</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B44">
+        <v>11281082.728478856</v>
+      </c>
+      <c r="C44">
+        <v>249729.0022676296</v>
+      </c>
+      <c r="D44">
+        <v>3635582.7284788573</v>
+      </c>
+      <c r="G44">
+        <v>2024418.7828548015</v>
+      </c>
+      <c r="H44">
+        <v>2081131.9534615683</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Türev Yükümlülüklerdeki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v xml:space="preserve">    Devlet Teşvik ve Yardımlarındaki Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
+      </c>
+      <c r="B47">
+        <v>-9670808.406474913</v>
+      </c>
+      <c r="C47">
+        <v>8306970.585275246</v>
+      </c>
+      <c r="D47">
+        <v>-871470.4064749123</v>
+      </c>
+      <c r="G47">
+        <v>24592684.316010553</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
+      </c>
+      <c r="B48">
+        <v>11481117.201393336</v>
+      </c>
+      <c r="C48">
+        <v>-989623.7235873975</v>
+      </c>
+      <c r="D48">
+        <v>-15839817.798606666</v>
+      </c>
+      <c r="G48">
+        <v>-7711175.344773713</v>
+      </c>
+      <c r="H48">
+        <v>-583417.9010321953</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+      <c r="B54">
+        <v>-72358769.86924674</v>
+      </c>
+      <c r="C54">
+        <v>-77323012.08191426</v>
+      </c>
+      <c r="D54">
+        <v>-59995428.869246736</v>
+      </c>
+      <c r="G54">
+        <v>-420285.10360371904</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Kira Ödemeleri</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">    Alınan Kira</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve/veya Müşterek Faaliyetlerin Sermaye Artırımına Katılımdan Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-33721739.3844735</v>
+      </c>
+      <c r="C67">
+        <v>150762999.1038939</v>
+      </c>
+      <c r="D67">
+        <v>470861043.6155265</v>
+      </c>
+      <c r="G67">
+        <v>-448489352.3378327</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="G78">
+        <v>-571026.0261506545</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="D98">
+        <v>470861043.6155265</v>
+      </c>
+      <c r="G98">
+        <v>-448489352.3378327</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>1638041373.343826</v>
+      </c>
+      <c r="C101">
+        <v>-278314718.1304339</v>
+      </c>
+      <c r="D101">
+        <v>-420695329.656174</v>
+      </c>
+      <c r="G101">
+        <v>-26619976.440565534</v>
+      </c>
+      <c r="H101">
+        <v>-280958.6487206414</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+      </c>
+      <c r="G106">
+        <v>113195600.09901904</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>-410649493.8678893</v>
+      </c>
+      <c r="C110">
+        <v>-291149387.06488985</v>
+      </c>
+      <c r="D110">
+        <v>-414046011.8678893</v>
+      </c>
+      <c r="G110">
+        <v>-83385537.25179932</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-13764477.046538431</v>
+      </c>
+      <c r="C118">
+        <v>-22381544.237903766</v>
+      </c>
+      <c r="D118">
+        <v>-19620012.04653843</v>
+      </c>
+      <c r="G118">
+        <v>-61340879.36354789</v>
+      </c>
+      <c r="H118">
+        <v>-280958.6487206414</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+      <c r="B119">
+        <v>239358765.25825372</v>
+      </c>
+      <c r="C119">
+        <v>35216213.17235966</v>
+      </c>
+      <c r="D119">
+        <v>12970694.258253722</v>
+      </c>
+      <c r="G119">
+        <v>4910840.075762621</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>2136302214.6051788</v>
+      </c>
+      <c r="C127">
+        <v>528269278.8365728</v>
+      </c>
+      <c r="D127">
+        <v>76827093.60517891</v>
+      </c>
+      <c r="G127">
+        <v>22301969.170299415</v>
+      </c>
+      <c r="H127">
+        <v>287920.6143482827</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H129"/>
   </ignoredErrors>
 </worksheet>
 </file>